--- a/DECISION/국장_방산_분석.xlsx
+++ b/DECISION/국장_방산_분석.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="30">
   <si>
     <t>날짜</t>
   </si>
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2025-12-06</t>
+    <t>2025-12-10</t>
   </si>
   <si>
     <t>HANWHA AEROSPACE</t>
@@ -95,6 +95,9 @@
   </si>
   <si>
     <t>Pattern</t>
+  </si>
+  <si>
+    <t>📈 매수 관찰 구간입니다.</t>
   </si>
   <si>
     <t>⛔ 관망하십시오.</t>
@@ -519,19 +522,19 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>895000</v>
+        <v>960000</v>
       </c>
       <c r="E2">
-        <v>37</v>
+        <v>58.7</v>
       </c>
       <c r="F2">
-        <v>5.05</v>
+        <v>16.5</v>
       </c>
       <c r="G2">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H2">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="I2">
         <v>76</v>
@@ -540,7 +543,7 @@
         <v>66</v>
       </c>
       <c r="K2">
-        <v>55.1</v>
+        <v>62.8</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -549,10 +552,10 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>52.28493729186943</v>
+        <v>48.11568981226033</v>
       </c>
       <c r="O2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -566,28 +569,28 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>182000</v>
+        <v>192200</v>
       </c>
       <c r="E3">
-        <v>36.5</v>
+        <v>54.9</v>
       </c>
       <c r="F3">
-        <v>3.59</v>
+        <v>13.39</v>
       </c>
       <c r="G3">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H3">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="I3">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="J3">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K3">
-        <v>51.1</v>
+        <v>61.4</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
@@ -596,10 +599,10 @@
         <v>27</v>
       </c>
       <c r="N3">
-        <v>52.28493729186943</v>
+        <v>48.11568981226033</v>
       </c>
       <c r="O3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -613,40 +616,40 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>106200</v>
+        <v>109000</v>
       </c>
       <c r="E4">
-        <v>40.6</v>
+        <v>54.5</v>
       </c>
       <c r="F4">
-        <v>-2.48</v>
+        <v>3.42</v>
       </c>
       <c r="G4">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H4">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="I4">
+        <v>56</v>
+      </c>
+      <c r="J4">
         <v>63</v>
       </c>
-      <c r="J4">
-        <v>66</v>
-      </c>
       <c r="K4">
-        <v>46.9</v>
+        <v>51.8</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
       </c>
       <c r="M4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N4">
-        <v>52.28493729186943</v>
+        <v>48.11568981226033</v>
       </c>
       <c r="O4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -660,40 +663,40 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>47200</v>
+        <v>48350</v>
       </c>
       <c r="E5">
-        <v>25.6</v>
+        <v>41.3</v>
       </c>
       <c r="F5">
-        <v>2.16</v>
+        <v>6.15</v>
       </c>
       <c r="G5">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H5">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="I5">
         <v>60</v>
       </c>
       <c r="J5">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K5">
-        <v>45.7</v>
+        <v>50.4</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
       </c>
       <c r="M5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N5">
-        <v>52.28493729186943</v>
+        <v>48.11568981226033</v>
       </c>
       <c r="O5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -707,40 +710,40 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>372500</v>
+        <v>388500</v>
       </c>
       <c r="E6">
-        <v>29.6</v>
+        <v>42.1</v>
       </c>
       <c r="F6">
-        <v>-2.74</v>
+        <v>6.58</v>
       </c>
       <c r="G6">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="H6">
         <v>56</v>
       </c>
       <c r="I6">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="J6">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="K6">
-        <v>37.1</v>
+        <v>42.4</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
       </c>
       <c r="M6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N6">
-        <v>52.28493729186943</v>
+        <v>48.11568981226033</v>
       </c>
       <c r="O6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/DECISION/국장_방산_분석.xlsx
+++ b/DECISION/국장_방산_분석.xlsx
@@ -64,12 +64,12 @@
     <t>2025-12-10</t>
   </si>
   <si>
+    <t>HYUNDAI ROTEM</t>
+  </si>
+  <si>
     <t>HANWHA AEROSPACE</t>
   </si>
   <si>
-    <t>HYUNDAI ROTEM</t>
-  </si>
-  <si>
     <t>KOREA AEROSPACE</t>
   </si>
   <si>
@@ -79,10 +79,10 @@
     <t>LIG Nex1</t>
   </si>
   <si>
+    <t>064350.KS</t>
+  </si>
+  <si>
     <t>012450.KS</t>
-  </si>
-  <si>
-    <t>064350.KS</t>
   </si>
   <si>
     <t>047810.KS</t>
@@ -522,28 +522,28 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>960000</v>
+        <v>188600</v>
       </c>
       <c r="E2">
-        <v>58.7</v>
+        <v>48.7</v>
       </c>
       <c r="F2">
-        <v>16.5</v>
+        <v>8.02</v>
       </c>
       <c r="G2">
         <v>60</v>
       </c>
       <c r="H2">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="I2">
         <v>76</v>
       </c>
       <c r="J2">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="K2">
-        <v>62.8</v>
+        <v>62.3</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -552,7 +552,7 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>48.11568981226033</v>
+        <v>46.17217538625081</v>
       </c>
       <c r="O2" t="s">
         <v>29</v>
@@ -569,37 +569,37 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>192200</v>
+        <v>926000</v>
       </c>
       <c r="E3">
-        <v>54.9</v>
+        <v>51.5</v>
       </c>
       <c r="F3">
-        <v>13.39</v>
+        <v>6.93</v>
       </c>
       <c r="G3">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H3">
+        <v>60</v>
+      </c>
+      <c r="I3">
         <v>66</v>
       </c>
-      <c r="I3">
-        <v>80</v>
-      </c>
       <c r="J3">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="K3">
-        <v>61.4</v>
+        <v>58.3</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
       </c>
       <c r="M3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N3">
-        <v>48.11568981226033</v>
+        <v>46.17217538625081</v>
       </c>
       <c r="O3" t="s">
         <v>29</v>
@@ -616,28 +616,28 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>109000</v>
+        <v>110600</v>
       </c>
       <c r="E4">
-        <v>54.5</v>
+        <v>56.5</v>
       </c>
       <c r="F4">
-        <v>3.42</v>
+        <v>3.08</v>
       </c>
       <c r="G4">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H4">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="I4">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="J4">
         <v>63</v>
       </c>
       <c r="K4">
-        <v>51.8</v>
+        <v>53.1</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
@@ -646,7 +646,7 @@
         <v>28</v>
       </c>
       <c r="N4">
-        <v>48.11568981226033</v>
+        <v>46.17217538625081</v>
       </c>
       <c r="O4" t="s">
         <v>29</v>
@@ -663,28 +663,28 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>48350</v>
+        <v>48100</v>
       </c>
       <c r="E5">
-        <v>41.3</v>
+        <v>38.7</v>
       </c>
       <c r="F5">
-        <v>6.15</v>
+        <v>2.78</v>
       </c>
       <c r="G5">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H5">
         <v>63</v>
       </c>
       <c r="I5">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="J5">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="K5">
-        <v>50.4</v>
+        <v>49.3</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
@@ -693,7 +693,7 @@
         <v>28</v>
       </c>
       <c r="N5">
-        <v>48.11568981226033</v>
+        <v>46.17217538625081</v>
       </c>
       <c r="O5" t="s">
         <v>29</v>
@@ -710,28 +710,28 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>388500</v>
+        <v>384000</v>
       </c>
       <c r="E6">
-        <v>42.1</v>
+        <v>35</v>
       </c>
       <c r="F6">
-        <v>6.58</v>
+        <v>2.54</v>
       </c>
       <c r="G6">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H6">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="I6">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J6">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="K6">
-        <v>42.4</v>
+        <v>42.9</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
@@ -740,7 +740,7 @@
         <v>28</v>
       </c>
       <c r="N6">
-        <v>48.11568981226033</v>
+        <v>46.17217538625081</v>
       </c>
       <c r="O6" t="s">
         <v>29</v>

--- a/DECISION/국장_방산_분석.xlsx
+++ b/DECISION/국장_방산_분석.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="29">
   <si>
     <t>날짜</t>
   </si>
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2025-12-10</t>
+    <t>2025-12-15</t>
   </si>
   <si>
     <t>HYUNDAI ROTEM</t>
@@ -95,9 +95,6 @@
   </si>
   <si>
     <t>Pattern</t>
-  </si>
-  <si>
-    <t>📈 매수 관찰 구간입니다.</t>
   </si>
   <si>
     <t>⛔ 관망하십시오.</t>
@@ -522,28 +519,28 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>188600</v>
+        <v>186400</v>
       </c>
       <c r="E2">
-        <v>48.7</v>
+        <v>60</v>
       </c>
       <c r="F2">
-        <v>8.02</v>
+        <v>2.42</v>
       </c>
       <c r="G2">
         <v>60</v>
       </c>
       <c r="H2">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="I2">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="J2">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="K2">
-        <v>62.3</v>
+        <v>58.6</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -552,10 +549,10 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>46.17217538625081</v>
+        <v>47.37006702605126</v>
       </c>
       <c r="O2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -569,40 +566,40 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>926000</v>
+        <v>961000</v>
       </c>
       <c r="E3">
-        <v>51.5</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="F3">
-        <v>6.93</v>
+        <v>7.37</v>
       </c>
       <c r="G3">
         <v>60</v>
       </c>
       <c r="H3">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="I3">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="J3">
         <v>56</v>
       </c>
       <c r="K3">
-        <v>58.3</v>
+        <v>57.4</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
       </c>
       <c r="M3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N3">
+        <v>47.37006702605126</v>
+      </c>
+      <c r="O3" t="s">
         <v>28</v>
-      </c>
-      <c r="N3">
-        <v>46.17217538625081</v>
-      </c>
-      <c r="O3" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -616,40 +613,40 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>110600</v>
+        <v>115100</v>
       </c>
       <c r="E4">
-        <v>56.5</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="F4">
-        <v>3.08</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="G4">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="H4">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="I4">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="J4">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K4">
-        <v>53.1</v>
+        <v>51.4</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
       </c>
       <c r="M4" t="s">
+        <v>27</v>
+      </c>
+      <c r="N4">
+        <v>47.37006702605126</v>
+      </c>
+      <c r="O4" t="s">
         <v>28</v>
-      </c>
-      <c r="N4">
-        <v>46.17217538625081</v>
-      </c>
-      <c r="O4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -663,40 +660,40 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>48100</v>
+        <v>53100</v>
       </c>
       <c r="E5">
-        <v>38.7</v>
+        <v>70.8</v>
       </c>
       <c r="F5">
-        <v>2.78</v>
+        <v>12.5</v>
       </c>
       <c r="G5">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H5">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="I5">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="J5">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="K5">
-        <v>49.3</v>
+        <v>50.2</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
       </c>
       <c r="M5" t="s">
+        <v>27</v>
+      </c>
+      <c r="N5">
+        <v>47.37006702605126</v>
+      </c>
+      <c r="O5" t="s">
         <v>28</v>
-      </c>
-      <c r="N5">
-        <v>46.17217538625081</v>
-      </c>
-      <c r="O5" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -710,19 +707,19 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>384000</v>
+        <v>383000</v>
       </c>
       <c r="E6">
-        <v>35</v>
+        <v>44.9</v>
       </c>
       <c r="F6">
-        <v>2.54</v>
+        <v>2.82</v>
       </c>
       <c r="G6">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H6">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="I6">
         <v>50</v>
@@ -731,19 +728,19 @@
         <v>46</v>
       </c>
       <c r="K6">
-        <v>42.9</v>
+        <v>46.2</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
       </c>
       <c r="M6" t="s">
+        <v>27</v>
+      </c>
+      <c r="N6">
+        <v>47.37006702605126</v>
+      </c>
+      <c r="O6" t="s">
         <v>28</v>
-      </c>
-      <c r="N6">
-        <v>46.17217538625081</v>
-      </c>
-      <c r="O6" t="s">
-        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/DECISION/국장_방산_분석.xlsx
+++ b/DECISION/국장_방산_분석.xlsx
@@ -61,37 +61,37 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2025-12-15</t>
+    <t>2025-12-29</t>
+  </si>
+  <si>
+    <t>HANWHA AEROSPACE</t>
   </si>
   <si>
     <t>HYUNDAI ROTEM</t>
   </si>
   <si>
-    <t>HANWHA AEROSPACE</t>
+    <t>HANWHA SYSTEMS</t>
+  </si>
+  <si>
+    <t>LIG Nex1</t>
   </si>
   <si>
     <t>KOREA AEROSPACE</t>
   </si>
   <si>
-    <t>HANWHA SYSTEMS</t>
-  </si>
-  <si>
-    <t>LIG Nex1</t>
+    <t>012450.KS</t>
   </si>
   <si>
     <t>064350.KS</t>
   </si>
   <si>
-    <t>012450.KS</t>
+    <t>272210.KS</t>
+  </si>
+  <si>
+    <t>079550.KS</t>
   </si>
   <si>
     <t>047810.KS</t>
-  </si>
-  <si>
-    <t>272210.KS</t>
-  </si>
-  <si>
-    <t>079550.KS</t>
   </si>
   <si>
     <t>Pattern</t>
@@ -519,28 +519,28 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>186400</v>
+        <v>949000</v>
       </c>
       <c r="E2">
-        <v>60</v>
+        <v>51.5</v>
       </c>
       <c r="F2">
-        <v>2.42</v>
+        <v>7.35</v>
       </c>
       <c r="G2">
         <v>60</v>
       </c>
       <c r="H2">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="I2">
         <v>66</v>
       </c>
       <c r="J2">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="K2">
-        <v>58.6</v>
+        <v>60</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -549,7 +549,7 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>47.37006702605126</v>
+        <v>51.940834218365</v>
       </c>
       <c r="O2" t="s">
         <v>28</v>
@@ -566,28 +566,28 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>961000</v>
+        <v>189600</v>
       </c>
       <c r="E3">
-        <v>64.90000000000001</v>
+        <v>48</v>
       </c>
       <c r="F3">
-        <v>7.37</v>
+        <v>5.74</v>
       </c>
       <c r="G3">
         <v>60</v>
       </c>
       <c r="H3">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="I3">
         <v>63</v>
       </c>
       <c r="J3">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="K3">
-        <v>57.4</v>
+        <v>58.8</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
@@ -596,7 +596,7 @@
         <v>27</v>
       </c>
       <c r="N3">
-        <v>47.37006702605126</v>
+        <v>51.940834218365</v>
       </c>
       <c r="O3" t="s">
         <v>28</v>
@@ -613,28 +613,28 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>115100</v>
+        <v>55400</v>
       </c>
       <c r="E4">
-        <v>71.09999999999999</v>
+        <v>64</v>
       </c>
       <c r="F4">
-        <v>8.380000000000001</v>
+        <v>2.03</v>
       </c>
       <c r="G4">
+        <v>60</v>
+      </c>
+      <c r="H4">
         <v>40</v>
       </c>
-      <c r="H4">
+      <c r="I4">
+        <v>56</v>
+      </c>
+      <c r="J4">
         <v>46</v>
       </c>
-      <c r="I4">
-        <v>63</v>
-      </c>
-      <c r="J4">
-        <v>73</v>
-      </c>
       <c r="K4">
-        <v>51.4</v>
+        <v>56</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
@@ -643,7 +643,7 @@
         <v>27</v>
       </c>
       <c r="N4">
-        <v>47.37006702605126</v>
+        <v>51.940834218365</v>
       </c>
       <c r="O4" t="s">
         <v>28</v>
@@ -660,28 +660,28 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>53100</v>
+        <v>431000</v>
       </c>
       <c r="E5">
-        <v>70.8</v>
+        <v>65.8</v>
       </c>
       <c r="F5">
-        <v>12.5</v>
+        <v>3.61</v>
       </c>
       <c r="G5">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H5">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="I5">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="J5">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K5">
-        <v>50.2</v>
+        <v>55.8</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
@@ -690,7 +690,7 @@
         <v>27</v>
       </c>
       <c r="N5">
-        <v>47.37006702605126</v>
+        <v>51.940834218365</v>
       </c>
       <c r="O5" t="s">
         <v>28</v>
@@ -707,28 +707,28 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>383000</v>
+        <v>117500</v>
       </c>
       <c r="E6">
-        <v>44.9</v>
+        <v>60.7</v>
       </c>
       <c r="F6">
-        <v>2.82</v>
+        <v>8</v>
       </c>
       <c r="G6">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H6">
+        <v>56</v>
+      </c>
+      <c r="I6">
+        <v>56</v>
+      </c>
+      <c r="J6">
         <v>60</v>
       </c>
-      <c r="I6">
-        <v>50</v>
-      </c>
-      <c r="J6">
-        <v>46</v>
-      </c>
       <c r="K6">
-        <v>46.2</v>
+        <v>53</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
@@ -737,7 +737,7 @@
         <v>27</v>
       </c>
       <c r="N6">
-        <v>47.37006702605126</v>
+        <v>51.940834218365</v>
       </c>
       <c r="O6" t="s">
         <v>28</v>

--- a/DECISION/국장_방산_분석.xlsx
+++ b/DECISION/국장_방산_분석.xlsx
@@ -61,37 +61,37 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2025-12-29</t>
+    <t>2026-01-05</t>
+  </si>
+  <si>
+    <t>LIG Nex1</t>
+  </si>
+  <si>
+    <t>HYUNDAI ROTEM</t>
   </si>
   <si>
     <t>HANWHA AEROSPACE</t>
   </si>
   <si>
-    <t>HYUNDAI ROTEM</t>
+    <t>KOREA AEROSPACE</t>
   </si>
   <si>
     <t>HANWHA SYSTEMS</t>
   </si>
   <si>
-    <t>LIG Nex1</t>
-  </si>
-  <si>
-    <t>KOREA AEROSPACE</t>
+    <t>079550.KS</t>
+  </si>
+  <si>
+    <t>064350.KS</t>
   </si>
   <si>
     <t>012450.KS</t>
   </si>
   <si>
-    <t>064350.KS</t>
+    <t>047810.KS</t>
   </si>
   <si>
     <t>272210.KS</t>
-  </si>
-  <si>
-    <t>079550.KS</t>
-  </si>
-  <si>
-    <t>047810.KS</t>
   </si>
   <si>
     <t>Pattern</t>
@@ -519,28 +519,28 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>949000</v>
+        <v>439000</v>
       </c>
       <c r="E2">
-        <v>51.5</v>
+        <v>67.7</v>
       </c>
       <c r="F2">
-        <v>7.35</v>
+        <v>5.28</v>
       </c>
       <c r="G2">
         <v>60</v>
       </c>
       <c r="H2">
+        <v>63</v>
+      </c>
+      <c r="I2">
+        <v>63</v>
+      </c>
+      <c r="J2">
         <v>56</v>
       </c>
-      <c r="I2">
-        <v>66</v>
-      </c>
-      <c r="J2">
-        <v>53</v>
-      </c>
       <c r="K2">
-        <v>60</v>
+        <v>55.7</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -549,7 +549,7 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>51.940834218365</v>
+        <v>41.50472307187444</v>
       </c>
       <c r="O2" t="s">
         <v>28</v>
@@ -566,28 +566,28 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>189600</v>
+        <v>193400</v>
       </c>
       <c r="E3">
-        <v>48</v>
+        <v>54.8</v>
       </c>
       <c r="F3">
-        <v>5.74</v>
+        <v>2.49</v>
       </c>
       <c r="G3">
         <v>60</v>
       </c>
       <c r="H3">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I3">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="J3">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="K3">
-        <v>58.8</v>
+        <v>54.5</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
@@ -596,7 +596,7 @@
         <v>27</v>
       </c>
       <c r="N3">
-        <v>51.940834218365</v>
+        <v>41.50472307187444</v>
       </c>
       <c r="O3" t="s">
         <v>28</v>
@@ -613,28 +613,28 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>55400</v>
+        <v>946000</v>
       </c>
       <c r="E4">
-        <v>64</v>
+        <v>53.2</v>
       </c>
       <c r="F4">
-        <v>2.03</v>
+        <v>5.11</v>
       </c>
       <c r="G4">
         <v>60</v>
       </c>
       <c r="H4">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="I4">
         <v>56</v>
       </c>
       <c r="J4">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="K4">
-        <v>56</v>
+        <v>52.9</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
@@ -643,7 +643,7 @@
         <v>27</v>
       </c>
       <c r="N4">
-        <v>51.940834218365</v>
+        <v>41.50472307187444</v>
       </c>
       <c r="O4" t="s">
         <v>28</v>
@@ -660,28 +660,28 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>431000</v>
+        <v>116800</v>
       </c>
       <c r="E5">
-        <v>65.8</v>
+        <v>59.8</v>
       </c>
       <c r="F5">
-        <v>3.61</v>
+        <v>2.64</v>
       </c>
       <c r="G5">
+        <v>60</v>
+      </c>
+      <c r="H5">
         <v>50</v>
       </c>
-      <c r="H5">
+      <c r="I5">
+        <v>50</v>
+      </c>
+      <c r="J5">
         <v>63</v>
       </c>
-      <c r="I5">
-        <v>63</v>
-      </c>
-      <c r="J5">
-        <v>56</v>
-      </c>
       <c r="K5">
-        <v>55.8</v>
+        <v>50.5</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
@@ -690,7 +690,7 @@
         <v>27</v>
       </c>
       <c r="N5">
-        <v>51.940834218365</v>
+        <v>41.50472307187444</v>
       </c>
       <c r="O5" t="s">
         <v>28</v>
@@ -707,28 +707,28 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>117500</v>
+        <v>55300</v>
       </c>
       <c r="E6">
-        <v>60.7</v>
+        <v>64.8</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>-5.95</v>
       </c>
       <c r="G6">
         <v>50</v>
       </c>
       <c r="H6">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="I6">
         <v>56</v>
       </c>
       <c r="J6">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="K6">
-        <v>53</v>
+        <v>49.9</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
@@ -737,7 +737,7 @@
         <v>27</v>
       </c>
       <c r="N6">
-        <v>51.940834218365</v>
+        <v>41.50472307187444</v>
       </c>
       <c r="O6" t="s">
         <v>28</v>

--- a/DECISION/국장_방산_분석.xlsx
+++ b/DECISION/국장_방산_분석.xlsx
@@ -61,37 +61,37 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-05</t>
+    <t>2026-01-07</t>
+  </si>
+  <si>
+    <t>HYUNDAI ROTEM</t>
+  </si>
+  <si>
+    <t>HANWHA SYSTEMS</t>
+  </si>
+  <si>
+    <t>HANWHA AEROSPACE</t>
   </si>
   <si>
     <t>LIG Nex1</t>
   </si>
   <si>
-    <t>HYUNDAI ROTEM</t>
-  </si>
-  <si>
-    <t>HANWHA AEROSPACE</t>
-  </si>
-  <si>
     <t>KOREA AEROSPACE</t>
   </si>
   <si>
-    <t>HANWHA SYSTEMS</t>
+    <t>064350.KS</t>
+  </si>
+  <si>
+    <t>272210.KS</t>
+  </si>
+  <si>
+    <t>012450.KS</t>
   </si>
   <si>
     <t>079550.KS</t>
   </si>
   <si>
-    <t>064350.KS</t>
-  </si>
-  <si>
-    <t>012450.KS</t>
-  </si>
-  <si>
     <t>047810.KS</t>
-  </si>
-  <si>
-    <t>272210.KS</t>
   </si>
   <si>
     <t>Pattern</t>
@@ -519,28 +519,28 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>439000</v>
+        <v>204000</v>
       </c>
       <c r="E2">
-        <v>67.7</v>
+        <v>68.3</v>
       </c>
       <c r="F2">
-        <v>5.28</v>
+        <v>7.59</v>
       </c>
       <c r="G2">
         <v>60</v>
       </c>
       <c r="H2">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="I2">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="J2">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="K2">
-        <v>55.7</v>
+        <v>59.5</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -549,7 +549,7 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>41.50472307187444</v>
+        <v>45.04298008974126</v>
       </c>
       <c r="O2" t="s">
         <v>28</v>
@@ -566,28 +566,28 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>193400</v>
+        <v>59100</v>
       </c>
       <c r="E3">
-        <v>54.8</v>
+        <v>62.1</v>
       </c>
       <c r="F3">
-        <v>2.49</v>
+        <v>6.68</v>
       </c>
       <c r="G3">
         <v>60</v>
       </c>
       <c r="H3">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="I3">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="J3">
         <v>56</v>
       </c>
       <c r="K3">
-        <v>54.5</v>
+        <v>56.7</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
@@ -596,7 +596,7 @@
         <v>27</v>
       </c>
       <c r="N3">
-        <v>41.50472307187444</v>
+        <v>45.04298008974126</v>
       </c>
       <c r="O3" t="s">
         <v>28</v>
@@ -613,28 +613,28 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>946000</v>
+        <v>1012000</v>
       </c>
       <c r="E4">
-        <v>53.2</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="F4">
-        <v>5.11</v>
+        <v>6.64</v>
       </c>
       <c r="G4">
         <v>60</v>
       </c>
       <c r="H4">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="I4">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="J4">
         <v>53</v>
       </c>
       <c r="K4">
-        <v>52.9</v>
+        <v>56.7</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
@@ -643,7 +643,7 @@
         <v>27</v>
       </c>
       <c r="N4">
-        <v>41.50472307187444</v>
+        <v>45.04298008974126</v>
       </c>
       <c r="O4" t="s">
         <v>28</v>
@@ -660,28 +660,28 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>116800</v>
+        <v>497000</v>
       </c>
       <c r="E5">
-        <v>59.8</v>
+        <v>78.5</v>
       </c>
       <c r="F5">
-        <v>2.64</v>
+        <v>15.31</v>
       </c>
       <c r="G5">
+        <v>40</v>
+      </c>
+      <c r="H5">
+        <v>66</v>
+      </c>
+      <c r="I5">
         <v>60</v>
       </c>
-      <c r="H5">
+      <c r="J5">
         <v>50</v>
       </c>
-      <c r="I5">
-        <v>50</v>
-      </c>
-      <c r="J5">
-        <v>63</v>
-      </c>
       <c r="K5">
-        <v>50.5</v>
+        <v>49.5</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
@@ -690,7 +690,7 @@
         <v>27</v>
       </c>
       <c r="N5">
-        <v>41.50472307187444</v>
+        <v>45.04298008974126</v>
       </c>
       <c r="O5" t="s">
         <v>28</v>
@@ -707,28 +707,28 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>55300</v>
+        <v>135200</v>
       </c>
       <c r="E6">
-        <v>64.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="F6">
-        <v>-5.95</v>
+        <v>15.06</v>
       </c>
       <c r="G6">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H6">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="I6">
         <v>56</v>
       </c>
       <c r="J6">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="K6">
-        <v>49.9</v>
+        <v>47.9</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
@@ -737,7 +737,7 @@
         <v>27</v>
       </c>
       <c r="N6">
-        <v>41.50472307187444</v>
+        <v>45.04298008974126</v>
       </c>
       <c r="O6" t="s">
         <v>28</v>

--- a/DECISION/국장_방산_분석.xlsx
+++ b/DECISION/국장_방산_분석.xlsx
@@ -519,13 +519,13 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>204000</v>
+        <v>201000</v>
       </c>
       <c r="E2">
-        <v>68.3</v>
+        <v>65.2</v>
       </c>
       <c r="F2">
-        <v>7.59</v>
+        <v>6.01</v>
       </c>
       <c r="G2">
         <v>60</v>
@@ -540,7 +540,7 @@
         <v>66</v>
       </c>
       <c r="K2">
-        <v>59.5</v>
+        <v>59.6</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -549,7 +549,7 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>45.04298008974126</v>
+        <v>45.26531441048893</v>
       </c>
       <c r="O2" t="s">
         <v>28</v>
@@ -566,28 +566,28 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>59100</v>
+        <v>58400</v>
       </c>
       <c r="E3">
-        <v>62.1</v>
+        <v>60.5</v>
       </c>
       <c r="F3">
-        <v>6.68</v>
+        <v>5.42</v>
       </c>
       <c r="G3">
         <v>60</v>
       </c>
       <c r="H3">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="I3">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="J3">
         <v>56</v>
       </c>
       <c r="K3">
-        <v>56.7</v>
+        <v>58</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
@@ -596,7 +596,7 @@
         <v>27</v>
       </c>
       <c r="N3">
-        <v>45.04298008974126</v>
+        <v>45.26531441048893</v>
       </c>
       <c r="O3" t="s">
         <v>28</v>
@@ -613,13 +613,13 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>1012000</v>
+        <v>997000</v>
       </c>
       <c r="E4">
-        <v>66.59999999999999</v>
+        <v>63.5</v>
       </c>
       <c r="F4">
-        <v>6.64</v>
+        <v>5.06</v>
       </c>
       <c r="G4">
         <v>60</v>
@@ -634,7 +634,7 @@
         <v>53</v>
       </c>
       <c r="K4">
-        <v>56.7</v>
+        <v>56.8</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
@@ -643,7 +643,7 @@
         <v>27</v>
       </c>
       <c r="N4">
-        <v>45.04298008974126</v>
+        <v>45.26531441048893</v>
       </c>
       <c r="O4" t="s">
         <v>28</v>
@@ -660,13 +660,13 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>497000</v>
+        <v>489500</v>
       </c>
       <c r="E5">
-        <v>78.5</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="F5">
-        <v>15.31</v>
+        <v>13.57</v>
       </c>
       <c r="G5">
         <v>40</v>
@@ -678,10 +678,10 @@
         <v>60</v>
       </c>
       <c r="J5">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="K5">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
@@ -690,7 +690,7 @@
         <v>27</v>
       </c>
       <c r="N5">
-        <v>45.04298008974126</v>
+        <v>45.26531441048893</v>
       </c>
       <c r="O5" t="s">
         <v>28</v>
@@ -707,13 +707,13 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>135200</v>
+        <v>134900</v>
       </c>
       <c r="E6">
-        <v>71.90000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="F6">
-        <v>15.06</v>
+        <v>14.81</v>
       </c>
       <c r="G6">
         <v>40</v>
@@ -728,7 +728,7 @@
         <v>63</v>
       </c>
       <c r="K6">
-        <v>47.9</v>
+        <v>48</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
@@ -737,7 +737,7 @@
         <v>27</v>
       </c>
       <c r="N6">
-        <v>45.04298008974126</v>
+        <v>45.26531441048893</v>
       </c>
       <c r="O6" t="s">
         <v>28</v>

--- a/DECISION/국장_방산_분석.xlsx
+++ b/DECISION/국장_방산_분석.xlsx
@@ -61,37 +61,37 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-07</t>
+    <t>2026-01-08</t>
+  </si>
+  <si>
+    <t>HANWHA SYSTEMS</t>
   </si>
   <si>
     <t>HYUNDAI ROTEM</t>
   </si>
   <si>
-    <t>HANWHA SYSTEMS</t>
+    <t>KOREA AEROSPACE</t>
+  </si>
+  <si>
+    <t>LIG Nex1</t>
   </si>
   <si>
     <t>HANWHA AEROSPACE</t>
   </si>
   <si>
-    <t>LIG Nex1</t>
-  </si>
-  <si>
-    <t>KOREA AEROSPACE</t>
+    <t>272210.KS</t>
   </si>
   <si>
     <t>064350.KS</t>
   </si>
   <si>
-    <t>272210.KS</t>
+    <t>047810.KS</t>
+  </si>
+  <si>
+    <t>079550.KS</t>
   </si>
   <si>
     <t>012450.KS</t>
-  </si>
-  <si>
-    <t>079550.KS</t>
-  </si>
-  <si>
-    <t>047810.KS</t>
   </si>
   <si>
     <t>Pattern</t>
@@ -519,28 +519,28 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>201000</v>
+        <v>60300</v>
       </c>
       <c r="E2">
-        <v>65.2</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="F2">
-        <v>6.01</v>
+        <v>10.85</v>
       </c>
       <c r="G2">
         <v>60</v>
       </c>
       <c r="H2">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="I2">
         <v>70</v>
       </c>
       <c r="J2">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="K2">
-        <v>59.6</v>
+        <v>59.1</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -549,7 +549,7 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>45.26531441048893</v>
+        <v>43.60821037092016</v>
       </c>
       <c r="O2" t="s">
         <v>28</v>
@@ -566,28 +566,28 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>58400</v>
+        <v>211000</v>
       </c>
       <c r="E3">
-        <v>60.5</v>
+        <v>70.7</v>
       </c>
       <c r="F3">
-        <v>5.42</v>
+        <v>12.29</v>
       </c>
       <c r="G3">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="H3">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="I3">
         <v>66</v>
       </c>
       <c r="J3">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="K3">
-        <v>58</v>
+        <v>51.5</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
@@ -596,7 +596,7 @@
         <v>27</v>
       </c>
       <c r="N3">
-        <v>45.26531441048893</v>
+        <v>43.60821037092016</v>
       </c>
       <c r="O3" t="s">
         <v>28</v>
@@ -613,28 +613,28 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>997000</v>
+        <v>142800</v>
       </c>
       <c r="E4">
-        <v>63.5</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="F4">
-        <v>5.06</v>
+        <v>24.83</v>
       </c>
       <c r="G4">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="H4">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="I4">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="J4">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K4">
-        <v>56.8</v>
+        <v>47.5</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
@@ -643,7 +643,7 @@
         <v>27</v>
       </c>
       <c r="N4">
-        <v>45.26531441048893</v>
+        <v>43.60821037092016</v>
       </c>
       <c r="O4" t="s">
         <v>28</v>
@@ -660,28 +660,28 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>489500</v>
+        <v>531000</v>
       </c>
       <c r="E5">
-        <v>76.09999999999999</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="F5">
-        <v>13.57</v>
+        <v>26.13</v>
       </c>
       <c r="G5">
         <v>40</v>
       </c>
       <c r="H5">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="I5">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="J5">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="K5">
-        <v>49.6</v>
+        <v>47.5</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
@@ -690,7 +690,7 @@
         <v>27</v>
       </c>
       <c r="N5">
-        <v>45.26531441048893</v>
+        <v>43.60821037092016</v>
       </c>
       <c r="O5" t="s">
         <v>28</v>
@@ -707,28 +707,28 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>134900</v>
+        <v>1090000</v>
       </c>
       <c r="E6">
-        <v>71.5</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="F6">
-        <v>14.81</v>
+        <v>15.83</v>
       </c>
       <c r="G6">
         <v>40</v>
       </c>
       <c r="H6">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="I6">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="J6">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="K6">
-        <v>48</v>
+        <v>46.3</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
@@ -737,7 +737,7 @@
         <v>27</v>
       </c>
       <c r="N6">
-        <v>45.26531441048893</v>
+        <v>43.60821037092016</v>
       </c>
       <c r="O6" t="s">
         <v>28</v>

--- a/DECISION/국장_방산_분석.xlsx
+++ b/DECISION/국장_방산_분석.xlsx
@@ -61,37 +61,37 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-08</t>
+    <t>2026-01-11</t>
+  </si>
+  <si>
+    <t>HYUNDAI ROTEM</t>
+  </si>
+  <si>
+    <t>HANWHA AEROSPACE</t>
+  </si>
+  <si>
+    <t>LIG Nex1</t>
+  </si>
+  <si>
+    <t>KOREA AEROSPACE</t>
   </si>
   <si>
     <t>HANWHA SYSTEMS</t>
   </si>
   <si>
-    <t>HYUNDAI ROTEM</t>
-  </si>
-  <si>
-    <t>KOREA AEROSPACE</t>
-  </si>
-  <si>
-    <t>LIG Nex1</t>
-  </si>
-  <si>
-    <t>HANWHA AEROSPACE</t>
+    <t>064350.KS</t>
+  </si>
+  <si>
+    <t>012450.KS</t>
+  </si>
+  <si>
+    <t>079550.KS</t>
+  </si>
+  <si>
+    <t>047810.KS</t>
   </si>
   <si>
     <t>272210.KS</t>
-  </si>
-  <si>
-    <t>064350.KS</t>
-  </si>
-  <si>
-    <t>047810.KS</t>
-  </si>
-  <si>
-    <t>079550.KS</t>
-  </si>
-  <si>
-    <t>012450.KS</t>
   </si>
   <si>
     <t>Pattern</t>
@@ -519,28 +519,28 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>60300</v>
+        <v>219000</v>
       </c>
       <c r="E2">
-        <v>68.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="F2">
-        <v>10.85</v>
+        <v>13.24</v>
       </c>
       <c r="G2">
+        <v>40</v>
+      </c>
+      <c r="H2">
         <v>60</v>
       </c>
-      <c r="H2">
-        <v>53</v>
-      </c>
       <c r="I2">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="J2">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K2">
-        <v>59.1</v>
+        <v>56.3</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -549,7 +549,7 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>43.60821037092016</v>
+        <v>50.40292622392195</v>
       </c>
       <c r="O2" t="s">
         <v>28</v>
@@ -566,28 +566,28 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>211000</v>
+        <v>1214000</v>
       </c>
       <c r="E3">
-        <v>70.7</v>
+        <v>85.7</v>
       </c>
       <c r="F3">
-        <v>12.29</v>
+        <v>28.33</v>
       </c>
       <c r="G3">
         <v>40</v>
       </c>
       <c r="H3">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="I3">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="J3">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="K3">
-        <v>51.5</v>
+        <v>51.1</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
@@ -596,7 +596,7 @@
         <v>27</v>
       </c>
       <c r="N3">
-        <v>43.60821037092016</v>
+        <v>50.40292622392195</v>
       </c>
       <c r="O3" t="s">
         <v>28</v>
@@ -613,28 +613,28 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>142800</v>
+        <v>542000</v>
       </c>
       <c r="E4">
-        <v>82.40000000000001</v>
+        <v>83.8</v>
       </c>
       <c r="F4">
-        <v>24.83</v>
+        <v>23.46</v>
       </c>
       <c r="G4">
         <v>40</v>
       </c>
       <c r="H4">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="I4">
         <v>56</v>
       </c>
       <c r="J4">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="K4">
-        <v>47.5</v>
+        <v>49.5</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
@@ -643,7 +643,7 @@
         <v>27</v>
       </c>
       <c r="N4">
-        <v>43.60821037092016</v>
+        <v>50.40292622392195</v>
       </c>
       <c r="O4" t="s">
         <v>28</v>
@@ -660,13 +660,13 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>531000</v>
+        <v>149800</v>
       </c>
       <c r="E5">
-        <v>83.59999999999999</v>
+        <v>87.2</v>
       </c>
       <c r="F5">
-        <v>26.13</v>
+        <v>28.25</v>
       </c>
       <c r="G5">
         <v>40</v>
@@ -675,13 +675,13 @@
         <v>63</v>
       </c>
       <c r="I5">
+        <v>53</v>
+      </c>
+      <c r="J5">
         <v>56</v>
       </c>
-      <c r="J5">
-        <v>50</v>
-      </c>
       <c r="K5">
-        <v>47.5</v>
+        <v>48.3</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
@@ -690,7 +690,7 @@
         <v>27</v>
       </c>
       <c r="N5">
-        <v>43.60821037092016</v>
+        <v>50.40292622392195</v>
       </c>
       <c r="O5" t="s">
         <v>28</v>
@@ -707,28 +707,28 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>1090000</v>
+        <v>76900</v>
       </c>
       <c r="E6">
-        <v>79.59999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="F6">
-        <v>15.83</v>
+        <v>39.06</v>
       </c>
       <c r="G6">
         <v>40</v>
       </c>
       <c r="H6">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="I6">
         <v>53</v>
       </c>
       <c r="J6">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K6">
-        <v>46.3</v>
+        <v>48.3</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
@@ -737,7 +737,7 @@
         <v>27</v>
       </c>
       <c r="N6">
-        <v>43.60821037092016</v>
+        <v>50.40292622392195</v>
       </c>
       <c r="O6" t="s">
         <v>28</v>

--- a/DECISION/국장_방산_분석.xlsx
+++ b/DECISION/국장_방산_분석.xlsx
@@ -61,37 +61,37 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-11</t>
+    <t>2026-01-12</t>
+  </si>
+  <si>
+    <t>HANWHA AEROSPACE</t>
   </si>
   <si>
     <t>HYUNDAI ROTEM</t>
   </si>
   <si>
-    <t>HANWHA AEROSPACE</t>
-  </si>
-  <si>
     <t>LIG Nex1</t>
   </si>
   <si>
+    <t>HANWHA SYSTEMS</t>
+  </si>
+  <si>
     <t>KOREA AEROSPACE</t>
   </si>
   <si>
-    <t>HANWHA SYSTEMS</t>
+    <t>012450.KS</t>
   </si>
   <si>
     <t>064350.KS</t>
   </si>
   <si>
-    <t>012450.KS</t>
-  </si>
-  <si>
     <t>079550.KS</t>
   </si>
   <si>
+    <t>272210.KS</t>
+  </si>
+  <si>
     <t>047810.KS</t>
-  </si>
-  <si>
-    <t>272210.KS</t>
   </si>
   <si>
     <t>Pattern</t>
@@ -519,25 +519,25 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>219000</v>
+        <v>1223000</v>
       </c>
       <c r="E2">
-        <v>74.7</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="F2">
-        <v>13.24</v>
+        <v>20.85</v>
       </c>
       <c r="G2">
         <v>40</v>
       </c>
       <c r="H2">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="I2">
         <v>73</v>
       </c>
       <c r="J2">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="K2">
         <v>56.3</v>
@@ -549,7 +549,7 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>50.40292622392195</v>
+        <v>50.43822221555986</v>
       </c>
       <c r="O2" t="s">
         <v>28</v>
@@ -566,28 +566,28 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>1214000</v>
+        <v>222000</v>
       </c>
       <c r="E3">
-        <v>85.7</v>
+        <v>80.8</v>
       </c>
       <c r="F3">
-        <v>28.33</v>
+        <v>11.67</v>
       </c>
       <c r="G3">
         <v>40</v>
       </c>
       <c r="H3">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="I3">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="J3">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K3">
-        <v>51.1</v>
+        <v>55.1</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
@@ -596,7 +596,7 @@
         <v>27</v>
       </c>
       <c r="N3">
-        <v>50.40292622392195</v>
+        <v>50.43822221555986</v>
       </c>
       <c r="O3" t="s">
         <v>28</v>
@@ -613,28 +613,28 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>542000</v>
+        <v>571000</v>
       </c>
       <c r="E4">
-        <v>83.8</v>
+        <v>86.3</v>
       </c>
       <c r="F4">
-        <v>23.46</v>
+        <v>21.88</v>
       </c>
       <c r="G4">
         <v>40</v>
       </c>
       <c r="H4">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="I4">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="J4">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="K4">
-        <v>49.5</v>
+        <v>51.1</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
@@ -643,7 +643,7 @@
         <v>27</v>
       </c>
       <c r="N4">
-        <v>50.40292622392195</v>
+        <v>50.43822221555986</v>
       </c>
       <c r="O4" t="s">
         <v>28</v>
@@ -660,28 +660,28 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>149800</v>
+        <v>78100</v>
       </c>
       <c r="E5">
-        <v>87.2</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="F5">
-        <v>28.25</v>
+        <v>34.66</v>
       </c>
       <c r="G5">
         <v>40</v>
       </c>
       <c r="H5">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="I5">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="J5">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="K5">
-        <v>48.3</v>
+        <v>49.5</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
@@ -690,7 +690,7 @@
         <v>27</v>
       </c>
       <c r="N5">
-        <v>50.40292622392195</v>
+        <v>50.43822221555986</v>
       </c>
       <c r="O5" t="s">
         <v>28</v>
@@ -707,28 +707,28 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>76900</v>
+        <v>154400</v>
       </c>
       <c r="E6">
-        <v>81.90000000000001</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="F6">
-        <v>39.06</v>
+        <v>24.12</v>
       </c>
       <c r="G6">
         <v>40</v>
       </c>
       <c r="H6">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="I6">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="J6">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="K6">
-        <v>48.3</v>
+        <v>47.1</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
@@ -737,7 +737,7 @@
         <v>27</v>
       </c>
       <c r="N6">
-        <v>50.40292622392195</v>
+        <v>50.43822221555986</v>
       </c>
       <c r="O6" t="s">
         <v>28</v>

--- a/DECISION/국장_방산_분석.xlsx
+++ b/DECISION/국장_방산_분석.xlsx
@@ -64,12 +64,12 @@
     <t>2026-01-12</t>
   </si>
   <si>
+    <t>HYUNDAI ROTEM</t>
+  </si>
+  <si>
     <t>HANWHA AEROSPACE</t>
   </si>
   <si>
-    <t>HYUNDAI ROTEM</t>
-  </si>
-  <si>
     <t>LIG Nex1</t>
   </si>
   <si>
@@ -79,10 +79,10 @@
     <t>KOREA AEROSPACE</t>
   </si>
   <si>
+    <t>064350.KS</t>
+  </si>
+  <si>
     <t>012450.KS</t>
-  </si>
-  <si>
-    <t>064350.KS</t>
   </si>
   <si>
     <t>079550.KS</t>
@@ -519,28 +519,28 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>1223000</v>
+        <v>218000</v>
       </c>
       <c r="E2">
-        <v>89.40000000000001</v>
+        <v>79</v>
       </c>
       <c r="F2">
-        <v>20.85</v>
+        <v>9.66</v>
       </c>
       <c r="G2">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H2">
+        <v>70</v>
+      </c>
+      <c r="I2">
         <v>66</v>
       </c>
-      <c r="I2">
-        <v>73</v>
-      </c>
       <c r="J2">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="K2">
-        <v>56.3</v>
+        <v>56.6</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -549,7 +549,7 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>50.43822221555986</v>
+        <v>50.56766494832259</v>
       </c>
       <c r="O2" t="s">
         <v>28</v>
@@ -566,28 +566,28 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>222000</v>
+        <v>1212000</v>
       </c>
       <c r="E3">
-        <v>80.8</v>
+        <v>88.8</v>
       </c>
       <c r="F3">
-        <v>11.67</v>
+        <v>19.76</v>
       </c>
       <c r="G3">
         <v>40</v>
       </c>
       <c r="H3">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="I3">
         <v>70</v>
       </c>
       <c r="J3">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="K3">
-        <v>55.1</v>
+        <v>55.2</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
@@ -596,7 +596,7 @@
         <v>27</v>
       </c>
       <c r="N3">
-        <v>50.43822221555986</v>
+        <v>50.56766494832259</v>
       </c>
       <c r="O3" t="s">
         <v>28</v>
@@ -613,28 +613,28 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>571000</v>
+        <v>560000</v>
       </c>
       <c r="E4">
-        <v>86.3</v>
+        <v>85.7</v>
       </c>
       <c r="F4">
-        <v>21.88</v>
+        <v>19.53</v>
       </c>
       <c r="G4">
         <v>40</v>
       </c>
       <c r="H4">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I4">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="J4">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="K4">
-        <v>51.1</v>
+        <v>49.6</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
@@ -643,7 +643,7 @@
         <v>27</v>
       </c>
       <c r="N4">
-        <v>50.43822221555986</v>
+        <v>50.56766494832259</v>
       </c>
       <c r="O4" t="s">
         <v>28</v>
@@ -660,13 +660,13 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>78100</v>
+        <v>77700</v>
       </c>
       <c r="E5">
-        <v>83.90000000000001</v>
+        <v>83.8</v>
       </c>
       <c r="F5">
-        <v>34.66</v>
+        <v>33.97</v>
       </c>
       <c r="G5">
         <v>40</v>
@@ -681,7 +681,7 @@
         <v>50</v>
       </c>
       <c r="K5">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
@@ -690,7 +690,7 @@
         <v>27</v>
       </c>
       <c r="N5">
-        <v>50.43822221555986</v>
+        <v>50.56766494832259</v>
       </c>
       <c r="O5" t="s">
         <v>28</v>
@@ -707,13 +707,13 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>154400</v>
+        <v>153900</v>
       </c>
       <c r="E6">
-        <v>87.59999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="F6">
-        <v>24.12</v>
+        <v>23.71</v>
       </c>
       <c r="G6">
         <v>40</v>
@@ -725,10 +725,10 @@
         <v>50</v>
       </c>
       <c r="J6">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="K6">
-        <v>47.1</v>
+        <v>47.2</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
@@ -737,7 +737,7 @@
         <v>27</v>
       </c>
       <c r="N6">
-        <v>50.43822221555986</v>
+        <v>50.56766494832259</v>
       </c>
       <c r="O6" t="s">
         <v>28</v>

--- a/DECISION/국장_방산_분석.xlsx
+++ b/DECISION/국장_방산_분석.xlsx
@@ -61,34 +61,34 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-12</t>
+    <t>2026-01-13</t>
+  </si>
+  <si>
+    <t>HANWHA SYSTEMS</t>
+  </si>
+  <si>
+    <t>HANWHA AEROSPACE</t>
   </si>
   <si>
     <t>HYUNDAI ROTEM</t>
   </si>
   <si>
-    <t>HANWHA AEROSPACE</t>
-  </si>
-  <si>
     <t>LIG Nex1</t>
   </si>
   <si>
-    <t>HANWHA SYSTEMS</t>
-  </si>
-  <si>
     <t>KOREA AEROSPACE</t>
   </si>
   <si>
+    <t>272210.KS</t>
+  </si>
+  <si>
+    <t>012450.KS</t>
+  </si>
+  <si>
     <t>064350.KS</t>
   </si>
   <si>
-    <t>012450.KS</t>
-  </si>
-  <si>
     <t>079550.KS</t>
-  </si>
-  <si>
-    <t>272210.KS</t>
   </si>
   <si>
     <t>047810.KS</t>
@@ -519,28 +519,28 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>218000</v>
+        <v>88500</v>
       </c>
       <c r="E2">
-        <v>79</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="F2">
-        <v>9.66</v>
+        <v>46.77</v>
       </c>
       <c r="G2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H2">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="I2">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="J2">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="K2">
-        <v>56.6</v>
+        <v>58.4</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -549,7 +549,7 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>50.56766494832259</v>
+        <v>47.98314273412904</v>
       </c>
       <c r="O2" t="s">
         <v>28</v>
@@ -566,13 +566,13 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>1212000</v>
+        <v>1286000</v>
       </c>
       <c r="E3">
-        <v>88.8</v>
+        <v>89.7</v>
       </c>
       <c r="F3">
-        <v>19.76</v>
+        <v>25.83</v>
       </c>
       <c r="G3">
         <v>40</v>
@@ -581,13 +581,13 @@
         <v>66</v>
       </c>
       <c r="I3">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="J3">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K3">
-        <v>55.2</v>
+        <v>52.8</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
@@ -596,7 +596,7 @@
         <v>27</v>
       </c>
       <c r="N3">
-        <v>50.56766494832259</v>
+        <v>47.98314273412904</v>
       </c>
       <c r="O3" t="s">
         <v>28</v>
@@ -613,28 +613,28 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>560000</v>
+        <v>228000</v>
       </c>
       <c r="E4">
-        <v>85.7</v>
+        <v>80.5</v>
       </c>
       <c r="F4">
-        <v>19.53</v>
+        <v>10.41</v>
       </c>
       <c r="G4">
         <v>40</v>
       </c>
       <c r="H4">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="I4">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="J4">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="K4">
-        <v>49.6</v>
+        <v>51.6</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
@@ -643,7 +643,7 @@
         <v>27</v>
       </c>
       <c r="N4">
-        <v>50.56766494832259</v>
+        <v>47.98314273412904</v>
       </c>
       <c r="O4" t="s">
         <v>28</v>
@@ -660,28 +660,28 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>77700</v>
+        <v>567000</v>
       </c>
       <c r="E5">
-        <v>83.8</v>
+        <v>84</v>
       </c>
       <c r="F5">
-        <v>33.97</v>
+        <v>14.55</v>
       </c>
       <c r="G5">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H5">
+        <v>53</v>
+      </c>
+      <c r="I5">
         <v>50</v>
       </c>
-      <c r="I5">
-        <v>56</v>
-      </c>
       <c r="J5">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K5">
-        <v>49.6</v>
+        <v>49.4</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
@@ -690,7 +690,7 @@
         <v>27</v>
       </c>
       <c r="N5">
-        <v>50.56766494832259</v>
+        <v>47.98314273412904</v>
       </c>
       <c r="O5" t="s">
         <v>28</v>
@@ -707,28 +707,28 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>153900</v>
+        <v>157700</v>
       </c>
       <c r="E6">
-        <v>87.5</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="F6">
-        <v>23.71</v>
+        <v>15.87</v>
       </c>
       <c r="G6">
         <v>40</v>
       </c>
       <c r="H6">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="I6">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J6">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="K6">
-        <v>47.2</v>
+        <v>47.6</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
@@ -737,7 +737,7 @@
         <v>27</v>
       </c>
       <c r="N6">
-        <v>50.56766494832259</v>
+        <v>47.98314273412904</v>
       </c>
       <c r="O6" t="s">
         <v>28</v>

--- a/DECISION/국장_방산_분석.xlsx
+++ b/DECISION/국장_방산_분석.xlsx
@@ -61,37 +61,37 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-13</t>
+    <t>2026-01-14</t>
+  </si>
+  <si>
+    <t>HYUNDAI ROTEM</t>
   </si>
   <si>
     <t>HANWHA SYSTEMS</t>
   </si>
   <si>
+    <t>KOREA AEROSPACE</t>
+  </si>
+  <si>
     <t>HANWHA AEROSPACE</t>
   </si>
   <si>
-    <t>HYUNDAI ROTEM</t>
-  </si>
-  <si>
     <t>LIG Nex1</t>
   </si>
   <si>
-    <t>KOREA AEROSPACE</t>
+    <t>064350.KS</t>
   </si>
   <si>
     <t>272210.KS</t>
   </si>
   <si>
+    <t>047810.KS</t>
+  </si>
+  <si>
     <t>012450.KS</t>
   </si>
   <si>
-    <t>064350.KS</t>
-  </si>
-  <si>
     <t>079550.KS</t>
-  </si>
-  <si>
-    <t>047810.KS</t>
   </si>
   <si>
     <t>Pattern</t>
@@ -519,28 +519,28 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>88500</v>
+        <v>223000</v>
       </c>
       <c r="E2">
-        <v>85.59999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="F2">
-        <v>46.77</v>
+        <v>10.12</v>
       </c>
       <c r="G2">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H2">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="I2">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="J2">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="K2">
-        <v>58.4</v>
+        <v>57.1</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -549,7 +549,7 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>47.98314273412904</v>
+        <v>43.1153238131143</v>
       </c>
       <c r="O2" t="s">
         <v>28</v>
@@ -566,28 +566,28 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>1286000</v>
+        <v>88200</v>
       </c>
       <c r="E3">
-        <v>89.7</v>
+        <v>84</v>
       </c>
       <c r="F3">
-        <v>25.83</v>
+        <v>50.77</v>
       </c>
       <c r="G3">
         <v>40</v>
       </c>
       <c r="H3">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="I3">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="J3">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K3">
-        <v>52.8</v>
+        <v>54.1</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
@@ -596,7 +596,7 @@
         <v>27</v>
       </c>
       <c r="N3">
-        <v>47.98314273412904</v>
+        <v>43.1153238131143</v>
       </c>
       <c r="O3" t="s">
         <v>28</v>
@@ -613,28 +613,28 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>228000</v>
+        <v>154400</v>
       </c>
       <c r="E4">
-        <v>80.5</v>
+        <v>84</v>
       </c>
       <c r="F4">
-        <v>10.41</v>
+        <v>13.45</v>
       </c>
       <c r="G4">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H4">
+        <v>63</v>
+      </c>
+      <c r="I4">
         <v>60</v>
       </c>
-      <c r="I4">
-        <v>63</v>
-      </c>
       <c r="J4">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="K4">
-        <v>51.6</v>
+        <v>51.9</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
@@ -643,7 +643,7 @@
         <v>27</v>
       </c>
       <c r="N4">
-        <v>47.98314273412904</v>
+        <v>43.1153238131143</v>
       </c>
       <c r="O4" t="s">
         <v>28</v>
@@ -660,28 +660,28 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>567000</v>
+        <v>1269000</v>
       </c>
       <c r="E5">
-        <v>84</v>
+        <v>87.3</v>
       </c>
       <c r="F5">
-        <v>14.55</v>
+        <v>25.64</v>
       </c>
       <c r="G5">
         <v>50</v>
       </c>
       <c r="H5">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="I5">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="J5">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="K5">
-        <v>49.4</v>
+        <v>51.9</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
@@ -690,7 +690,7 @@
         <v>27</v>
       </c>
       <c r="N5">
-        <v>47.98314273412904</v>
+        <v>43.1153238131143</v>
       </c>
       <c r="O5" t="s">
         <v>28</v>
@@ -707,28 +707,28 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>157700</v>
+        <v>556000</v>
       </c>
       <c r="E6">
-        <v>89.09999999999999</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="F6">
-        <v>15.87</v>
+        <v>13.59</v>
       </c>
       <c r="G6">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H6">
+        <v>66</v>
+      </c>
+      <c r="I6">
         <v>56</v>
       </c>
-      <c r="I6">
-        <v>53</v>
-      </c>
       <c r="J6">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="K6">
-        <v>47.6</v>
+        <v>50.3</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
@@ -737,7 +737,7 @@
         <v>27</v>
       </c>
       <c r="N6">
-        <v>47.98314273412904</v>
+        <v>43.1153238131143</v>
       </c>
       <c r="O6" t="s">
         <v>28</v>

--- a/DECISION/국장_방산_분석.xlsx
+++ b/DECISION/국장_방산_분석.xlsx
@@ -61,34 +61,34 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-14</t>
+    <t>2026-01-17</t>
   </si>
   <si>
     <t>HYUNDAI ROTEM</t>
   </si>
   <si>
+    <t>KOREA AEROSPACE</t>
+  </si>
+  <si>
+    <t>HANWHA AEROSPACE</t>
+  </si>
+  <si>
     <t>HANWHA SYSTEMS</t>
   </si>
   <si>
-    <t>KOREA AEROSPACE</t>
-  </si>
-  <si>
-    <t>HANWHA AEROSPACE</t>
-  </si>
-  <si>
     <t>LIG Nex1</t>
   </si>
   <si>
     <t>064350.KS</t>
   </si>
   <si>
+    <t>047810.KS</t>
+  </si>
+  <si>
+    <t>012450.KS</t>
+  </si>
+  <si>
     <t>272210.KS</t>
-  </si>
-  <si>
-    <t>047810.KS</t>
-  </si>
-  <si>
-    <t>012450.KS</t>
   </si>
   <si>
     <t>079550.KS</t>
@@ -519,28 +519,28 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>223000</v>
+        <v>215000</v>
       </c>
       <c r="E2">
-        <v>72.40000000000001</v>
+        <v>68.2</v>
       </c>
       <c r="F2">
-        <v>10.12</v>
+        <v>-1.83</v>
       </c>
       <c r="G2">
         <v>50</v>
       </c>
       <c r="H2">
+        <v>56</v>
+      </c>
+      <c r="I2">
         <v>63</v>
       </c>
-      <c r="I2">
-        <v>73</v>
-      </c>
       <c r="J2">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="K2">
-        <v>57.1</v>
+        <v>52.3</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -549,7 +549,7 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>43.1153238131143</v>
+        <v>40.49436870247035</v>
       </c>
       <c r="O2" t="s">
         <v>28</v>
@@ -566,28 +566,28 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>88200</v>
+        <v>155900</v>
       </c>
       <c r="E3">
-        <v>84</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="F3">
-        <v>50.77</v>
+        <v>4.07</v>
       </c>
       <c r="G3">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H3">
+        <v>53</v>
+      </c>
+      <c r="I3">
         <v>60</v>
       </c>
-      <c r="I3">
-        <v>73</v>
-      </c>
       <c r="J3">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="K3">
-        <v>54.1</v>
+        <v>51.1</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
@@ -596,7 +596,7 @@
         <v>27</v>
       </c>
       <c r="N3">
-        <v>43.1153238131143</v>
+        <v>40.49436870247035</v>
       </c>
       <c r="O3" t="s">
         <v>28</v>
@@ -613,28 +613,28 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>154400</v>
+        <v>1299000</v>
       </c>
       <c r="E4">
-        <v>84</v>
+        <v>91.5</v>
       </c>
       <c r="F4">
-        <v>13.45</v>
+        <v>7</v>
       </c>
       <c r="G4">
         <v>50</v>
       </c>
       <c r="H4">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="I4">
         <v>60</v>
       </c>
       <c r="J4">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="K4">
-        <v>51.9</v>
+        <v>51.1</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
@@ -643,7 +643,7 @@
         <v>27</v>
       </c>
       <c r="N4">
-        <v>43.1153238131143</v>
+        <v>40.49436870247035</v>
       </c>
       <c r="O4" t="s">
         <v>28</v>
@@ -660,28 +660,28 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>1269000</v>
+        <v>90900</v>
       </c>
       <c r="E5">
-        <v>87.3</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="F5">
-        <v>25.64</v>
+        <v>18.21</v>
       </c>
       <c r="G5">
         <v>50</v>
       </c>
       <c r="H5">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="I5">
         <v>60</v>
       </c>
       <c r="J5">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="K5">
-        <v>51.9</v>
+        <v>51.1</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
@@ -690,7 +690,7 @@
         <v>27</v>
       </c>
       <c r="N5">
-        <v>43.1153238131143</v>
+        <v>40.49436870247035</v>
       </c>
       <c r="O5" t="s">
         <v>28</v>
@@ -707,28 +707,28 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>556000</v>
+        <v>535000</v>
       </c>
       <c r="E6">
-        <v>79.09999999999999</v>
+        <v>73.8</v>
       </c>
       <c r="F6">
-        <v>13.59</v>
+        <v>-1.29</v>
       </c>
       <c r="G6">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H6">
+        <v>60</v>
+      </c>
+      <c r="I6">
+        <v>60</v>
+      </c>
+      <c r="J6">
         <v>66</v>
       </c>
-      <c r="I6">
-        <v>56</v>
-      </c>
-      <c r="J6">
-        <v>63</v>
-      </c>
       <c r="K6">
-        <v>50.3</v>
+        <v>48.1</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
@@ -737,7 +737,7 @@
         <v>27</v>
       </c>
       <c r="N6">
-        <v>43.1153238131143</v>
+        <v>40.49436870247035</v>
       </c>
       <c r="O6" t="s">
         <v>28</v>

--- a/DECISION/국장_방산_분석.xlsx
+++ b/DECISION/국장_방산_분석.xlsx
@@ -61,37 +61,37 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-17</t>
+    <t>2026-01-19</t>
+  </si>
+  <si>
+    <t>LIG Nex1</t>
   </si>
   <si>
     <t>HYUNDAI ROTEM</t>
   </si>
   <si>
+    <t>HANWHA SYSTEMS</t>
+  </si>
+  <si>
+    <t>HANWHA AEROSPACE</t>
+  </si>
+  <si>
     <t>KOREA AEROSPACE</t>
   </si>
   <si>
-    <t>HANWHA AEROSPACE</t>
-  </si>
-  <si>
-    <t>HANWHA SYSTEMS</t>
-  </si>
-  <si>
-    <t>LIG Nex1</t>
+    <t>079550.KS</t>
   </si>
   <si>
     <t>064350.KS</t>
   </si>
   <si>
+    <t>272210.KS</t>
+  </si>
+  <si>
+    <t>012450.KS</t>
+  </si>
+  <si>
     <t>047810.KS</t>
-  </si>
-  <si>
-    <t>012450.KS</t>
-  </si>
-  <si>
-    <t>272210.KS</t>
-  </si>
-  <si>
-    <t>079550.KS</t>
   </si>
   <si>
     <t>Pattern</t>
@@ -519,28 +519,28 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>215000</v>
+        <v>554000</v>
       </c>
       <c r="E2">
-        <v>68.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="F2">
-        <v>-1.83</v>
+        <v>-1.07</v>
       </c>
       <c r="G2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H2">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="I2">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="J2">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="K2">
-        <v>52.3</v>
+        <v>50.5</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -549,7 +549,7 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>40.49436870247035</v>
+        <v>40.44495449250464</v>
       </c>
       <c r="O2" t="s">
         <v>28</v>
@@ -566,28 +566,28 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>155900</v>
+        <v>215000</v>
       </c>
       <c r="E3">
-        <v>75.40000000000001</v>
+        <v>71.3</v>
       </c>
       <c r="F3">
-        <v>4.07</v>
+        <v>-1.38</v>
       </c>
       <c r="G3">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H3">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="I3">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="J3">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="K3">
-        <v>51.1</v>
+        <v>50.5</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
@@ -596,7 +596,7 @@
         <v>27</v>
       </c>
       <c r="N3">
-        <v>40.49436870247035</v>
+        <v>40.44495449250464</v>
       </c>
       <c r="O3" t="s">
         <v>28</v>
@@ -613,28 +613,28 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>1299000</v>
+        <v>90800</v>
       </c>
       <c r="E4">
-        <v>91.5</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="F4">
-        <v>7</v>
+        <v>16.86</v>
       </c>
       <c r="G4">
         <v>50</v>
       </c>
       <c r="H4">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="I4">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="J4">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="K4">
-        <v>51.1</v>
+        <v>49.5</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
@@ -643,7 +643,7 @@
         <v>27</v>
       </c>
       <c r="N4">
-        <v>40.49436870247035</v>
+        <v>40.44495449250464</v>
       </c>
       <c r="O4" t="s">
         <v>28</v>
@@ -660,13 +660,13 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>90900</v>
+        <v>1330000</v>
       </c>
       <c r="E5">
-        <v>81.09999999999999</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="F5">
-        <v>18.21</v>
+        <v>9.74</v>
       </c>
       <c r="G5">
         <v>50</v>
@@ -675,13 +675,13 @@
         <v>53</v>
       </c>
       <c r="I5">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="J5">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="K5">
-        <v>51.1</v>
+        <v>48.3</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
@@ -690,7 +690,7 @@
         <v>27</v>
       </c>
       <c r="N5">
-        <v>40.49436870247035</v>
+        <v>40.44495449250464</v>
       </c>
       <c r="O5" t="s">
         <v>28</v>
@@ -707,28 +707,28 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>535000</v>
+        <v>165500</v>
       </c>
       <c r="E6">
-        <v>73.8</v>
+        <v>81.2</v>
       </c>
       <c r="F6">
-        <v>-1.29</v>
+        <v>7.54</v>
       </c>
       <c r="G6">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H6">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="I6">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J6">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="K6">
-        <v>48.1</v>
+        <v>47.1</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
@@ -737,7 +737,7 @@
         <v>27</v>
       </c>
       <c r="N6">
-        <v>40.49436870247035</v>
+        <v>40.44495449250464</v>
       </c>
       <c r="O6" t="s">
         <v>28</v>

--- a/DECISION/국장_방산_분석.xlsx
+++ b/DECISION/국장_방산_분석.xlsx
@@ -61,46 +61,46 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-19</t>
+    <t>2026-03-03</t>
+  </si>
+  <si>
+    <t>HANWHA AEROSPACE</t>
+  </si>
+  <si>
+    <t>HYUNDAI ROTEM</t>
   </si>
   <si>
     <t>LIG Nex1</t>
   </si>
   <si>
-    <t>HYUNDAI ROTEM</t>
+    <t>KOREA AEROSPACE</t>
   </si>
   <si>
     <t>HANWHA SYSTEMS</t>
   </si>
   <si>
-    <t>HANWHA AEROSPACE</t>
-  </si>
-  <si>
-    <t>KOREA AEROSPACE</t>
+    <t>012450.KS</t>
+  </si>
+  <si>
+    <t>064350.KS</t>
   </si>
   <si>
     <t>079550.KS</t>
   </si>
   <si>
-    <t>064350.KS</t>
+    <t>047810.KS</t>
   </si>
   <si>
     <t>272210.KS</t>
   </si>
   <si>
-    <t>012450.KS</t>
-  </si>
-  <si>
-    <t>047810.KS</t>
-  </si>
-  <si>
     <t>Pattern</t>
   </si>
   <si>
     <t>⛔ 관망하십시오.</t>
   </si>
   <si>
-    <t>⚪ 중립 구간</t>
+    <t>🔴 강한 긴축 / 리스크</t>
   </si>
 </sst>
 </file>
@@ -519,28 +519,28 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>554000</v>
+        <v>1432000</v>
       </c>
       <c r="E2">
-        <v>80.40000000000001</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="F2">
-        <v>-1.07</v>
+        <v>15.86</v>
       </c>
       <c r="G2">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H2">
+        <v>60</v>
+      </c>
+      <c r="I2">
         <v>63</v>
       </c>
-      <c r="I2">
-        <v>66</v>
-      </c>
       <c r="J2">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="K2">
-        <v>50.5</v>
+        <v>46.3</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -549,7 +549,7 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>40.44495449250464</v>
+        <v>20.49503599836755</v>
       </c>
       <c r="O2" t="s">
         <v>28</v>
@@ -566,19 +566,19 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>215000</v>
+        <v>249000</v>
       </c>
       <c r="E3">
-        <v>71.3</v>
+        <v>73.3</v>
       </c>
       <c r="F3">
-        <v>-1.38</v>
+        <v>12.42</v>
       </c>
       <c r="G3">
         <v>40</v>
       </c>
       <c r="H3">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="I3">
         <v>66</v>
@@ -587,7 +587,7 @@
         <v>70</v>
       </c>
       <c r="K3">
-        <v>50.5</v>
+        <v>44.5</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
@@ -596,7 +596,7 @@
         <v>27</v>
       </c>
       <c r="N3">
-        <v>40.44495449250464</v>
+        <v>20.49503599836755</v>
       </c>
       <c r="O3" t="s">
         <v>28</v>
@@ -613,28 +613,28 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>90800</v>
+        <v>661000</v>
       </c>
       <c r="E4">
-        <v>83.40000000000001</v>
+        <v>89.3</v>
       </c>
       <c r="F4">
-        <v>16.86</v>
+        <v>35.04</v>
       </c>
       <c r="G4">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H4">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="I4">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="J4">
         <v>53</v>
       </c>
       <c r="K4">
-        <v>49.5</v>
+        <v>44.5</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
@@ -643,7 +643,7 @@
         <v>27</v>
       </c>
       <c r="N4">
-        <v>40.44495449250464</v>
+        <v>20.49503599836755</v>
       </c>
       <c r="O4" t="s">
         <v>28</v>
@@ -660,28 +660,28 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>1330000</v>
+        <v>197600</v>
       </c>
       <c r="E5">
-        <v>93.40000000000001</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="F5">
-        <v>9.74</v>
+        <v>12.53</v>
       </c>
       <c r="G5">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H5">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="I5">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="J5">
-        <v>30</v>
+        <v>76</v>
       </c>
       <c r="K5">
-        <v>48.3</v>
+        <v>42.1</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
@@ -690,7 +690,7 @@
         <v>27</v>
       </c>
       <c r="N5">
-        <v>40.44495449250464</v>
+        <v>20.49503599836755</v>
       </c>
       <c r="O5" t="s">
         <v>28</v>
@@ -707,28 +707,28 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>165500</v>
+        <v>146700</v>
       </c>
       <c r="E6">
-        <v>81.2</v>
+        <v>73.3</v>
       </c>
       <c r="F6">
-        <v>7.54</v>
+        <v>31.81</v>
       </c>
       <c r="G6">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H6">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="I6">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="J6">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="K6">
-        <v>47.1</v>
+        <v>42.1</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
@@ -737,7 +737,7 @@
         <v>27</v>
       </c>
       <c r="N6">
-        <v>40.44495449250464</v>
+        <v>20.49503599836755</v>
       </c>
       <c r="O6" t="s">
         <v>28</v>

--- a/DECISION/국장_방산_분석.xlsx
+++ b/DECISION/국장_방산_분석.xlsx
@@ -61,37 +61,37 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-03-03</t>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>HANWHA SYSTEMS</t>
+  </si>
+  <si>
+    <t>HYUNDAI ROTEM</t>
+  </si>
+  <si>
+    <t>KOREA AEROSPACE</t>
   </si>
   <si>
     <t>HANWHA AEROSPACE</t>
   </si>
   <si>
-    <t>HYUNDAI ROTEM</t>
-  </si>
-  <si>
     <t>LIG Nex1</t>
   </si>
   <si>
-    <t>KOREA AEROSPACE</t>
-  </si>
-  <si>
-    <t>HANWHA SYSTEMS</t>
+    <t>272210.KS</t>
+  </si>
+  <si>
+    <t>064350.KS</t>
+  </si>
+  <si>
+    <t>047810.KS</t>
   </si>
   <si>
     <t>012450.KS</t>
   </si>
   <si>
-    <t>064350.KS</t>
-  </si>
-  <si>
     <t>079550.KS</t>
-  </si>
-  <si>
-    <t>047810.KS</t>
-  </si>
-  <si>
-    <t>272210.KS</t>
   </si>
   <si>
     <t>Pattern</t>
@@ -519,19 +519,19 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>1432000</v>
+        <v>172100</v>
       </c>
       <c r="E2">
-        <v>67.59999999999999</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="F2">
-        <v>15.86</v>
+        <v>51.5</v>
       </c>
       <c r="G2">
+        <v>40</v>
+      </c>
+      <c r="H2">
         <v>50</v>
-      </c>
-      <c r="H2">
-        <v>60</v>
       </c>
       <c r="I2">
         <v>63</v>
@@ -540,7 +540,7 @@
         <v>56</v>
       </c>
       <c r="K2">
-        <v>46.3</v>
+        <v>38.5</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -549,7 +549,7 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>20.49503599836755</v>
+        <v>4.469434098808478</v>
       </c>
       <c r="O2" t="s">
         <v>28</v>
@@ -566,28 +566,28 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>249000</v>
+        <v>233000</v>
       </c>
       <c r="E3">
-        <v>73.3</v>
+        <v>61</v>
       </c>
       <c r="F3">
-        <v>12.42</v>
+        <v>1.08</v>
       </c>
       <c r="G3">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="H3">
+        <v>46</v>
+      </c>
+      <c r="I3">
+        <v>46</v>
+      </c>
+      <c r="J3">
         <v>53</v>
       </c>
-      <c r="I3">
-        <v>66</v>
-      </c>
-      <c r="J3">
-        <v>70</v>
-      </c>
       <c r="K3">
-        <v>44.5</v>
+        <v>37.7</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
@@ -596,7 +596,7 @@
         <v>27</v>
       </c>
       <c r="N3">
-        <v>20.49503599836755</v>
+        <v>4.469434098808478</v>
       </c>
       <c r="O3" t="s">
         <v>28</v>
@@ -613,28 +613,28 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>661000</v>
+        <v>178600</v>
       </c>
       <c r="E4">
-        <v>89.3</v>
+        <v>57.2</v>
       </c>
       <c r="F4">
-        <v>35.04</v>
+        <v>-6.74</v>
       </c>
       <c r="G4">
         <v>40</v>
       </c>
       <c r="H4">
+        <v>56</v>
+      </c>
+      <c r="I4">
         <v>60</v>
       </c>
-      <c r="I4">
-        <v>66</v>
-      </c>
       <c r="J4">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="K4">
-        <v>44.5</v>
+        <v>37.3</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
@@ -643,7 +643,7 @@
         <v>27</v>
       </c>
       <c r="N4">
-        <v>20.49503599836755</v>
+        <v>4.469434098808478</v>
       </c>
       <c r="O4" t="s">
         <v>28</v>
@@ -660,28 +660,28 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>197600</v>
+        <v>1530000</v>
       </c>
       <c r="E5">
-        <v>82.40000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="F5">
-        <v>12.53</v>
+        <v>28.03</v>
       </c>
       <c r="G5">
         <v>40</v>
       </c>
       <c r="H5">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I5">
         <v>60</v>
       </c>
       <c r="J5">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="K5">
-        <v>42.1</v>
+        <v>37.3</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
@@ -690,7 +690,7 @@
         <v>27</v>
       </c>
       <c r="N5">
-        <v>20.49503599836755</v>
+        <v>4.469434098808478</v>
       </c>
       <c r="O5" t="s">
         <v>28</v>
@@ -707,28 +707,28 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>146700</v>
+        <v>877000</v>
       </c>
       <c r="E6">
-        <v>73.3</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="F6">
-        <v>31.81</v>
+        <v>72.3</v>
       </c>
       <c r="G6">
         <v>40</v>
       </c>
       <c r="H6">
+        <v>70</v>
+      </c>
+      <c r="I6">
+        <v>53</v>
+      </c>
+      <c r="J6">
         <v>40</v>
       </c>
-      <c r="I6">
-        <v>60</v>
-      </c>
-      <c r="J6">
-        <v>63</v>
-      </c>
       <c r="K6">
-        <v>42.1</v>
+        <v>34.5</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
@@ -737,7 +737,7 @@
         <v>27</v>
       </c>
       <c r="N6">
-        <v>20.49503599836755</v>
+        <v>4.469434098808478</v>
       </c>
       <c r="O6" t="s">
         <v>28</v>

--- a/DECISION/국장_방산_분석.xlsx
+++ b/DECISION/국장_방산_분석.xlsx
@@ -64,6 +64,9 @@
     <t>2026-03-09</t>
   </si>
   <si>
+    <t>HANWHA AEROSPACE</t>
+  </si>
+  <si>
     <t>HANWHA SYSTEMS</t>
   </si>
   <si>
@@ -73,12 +76,12 @@
     <t>KOREA AEROSPACE</t>
   </si>
   <si>
-    <t>HANWHA AEROSPACE</t>
-  </si>
-  <si>
     <t>LIG Nex1</t>
   </si>
   <si>
+    <t>012450.KS</t>
+  </si>
+  <si>
     <t>272210.KS</t>
   </si>
   <si>
@@ -86,9 +89,6 @@
   </si>
   <si>
     <t>047810.KS</t>
-  </si>
-  <si>
-    <t>012450.KS</t>
   </si>
   <si>
     <t>079550.KS</t>
@@ -519,28 +519,28 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>172100</v>
+        <v>1434000</v>
       </c>
       <c r="E2">
-        <v>73.59999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="F2">
-        <v>51.5</v>
+        <v>20</v>
       </c>
       <c r="G2">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="H2">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="I2">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="J2">
         <v>56</v>
       </c>
       <c r="K2">
-        <v>38.5</v>
+        <v>42</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -549,7 +549,7 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>4.469434098808478</v>
+        <v>0</v>
       </c>
       <c r="O2" t="s">
         <v>28</v>
@@ -566,28 +566,28 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>233000</v>
+        <v>162700</v>
       </c>
       <c r="E3">
-        <v>61</v>
+        <v>71.8</v>
       </c>
       <c r="F3">
-        <v>1.08</v>
+        <v>43.22</v>
       </c>
       <c r="G3">
+        <v>40</v>
+      </c>
+      <c r="H3">
+        <v>53</v>
+      </c>
+      <c r="I3">
         <v>60</v>
       </c>
-      <c r="H3">
-        <v>46</v>
-      </c>
-      <c r="I3">
-        <v>46</v>
-      </c>
       <c r="J3">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K3">
-        <v>37.7</v>
+        <v>36</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
@@ -596,7 +596,7 @@
         <v>27</v>
       </c>
       <c r="N3">
-        <v>4.469434098808478</v>
+        <v>0</v>
       </c>
       <c r="O3" t="s">
         <v>28</v>
@@ -613,28 +613,28 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>178600</v>
+        <v>215000</v>
       </c>
       <c r="E4">
-        <v>57.2</v>
+        <v>54</v>
       </c>
       <c r="F4">
-        <v>-6.74</v>
+        <v>-6.72</v>
       </c>
       <c r="G4">
         <v>40</v>
       </c>
       <c r="H4">
+        <v>50</v>
+      </c>
+      <c r="I4">
         <v>56</v>
-      </c>
-      <c r="I4">
-        <v>60</v>
       </c>
       <c r="J4">
         <v>60</v>
       </c>
       <c r="K4">
-        <v>37.3</v>
+        <v>34.4</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
@@ -643,7 +643,7 @@
         <v>27</v>
       </c>
       <c r="N4">
-        <v>4.469434098808478</v>
+        <v>0</v>
       </c>
       <c r="O4" t="s">
         <v>28</v>
@@ -660,16 +660,16 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>1530000</v>
+        <v>174100</v>
       </c>
       <c r="E5">
-        <v>75.8</v>
+        <v>55</v>
       </c>
       <c r="F5">
-        <v>28.03</v>
+        <v>-9.09</v>
       </c>
       <c r="G5">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H5">
         <v>60</v>
@@ -678,10 +678,10 @@
         <v>60</v>
       </c>
       <c r="J5">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K5">
-        <v>37.3</v>
+        <v>33</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
@@ -690,7 +690,7 @@
         <v>27</v>
       </c>
       <c r="N5">
-        <v>4.469434098808478</v>
+        <v>0</v>
       </c>
       <c r="O5" t="s">
         <v>28</v>
@@ -707,28 +707,28 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>877000</v>
+        <v>796000</v>
       </c>
       <c r="E6">
-        <v>88.59999999999999</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="F6">
-        <v>72.3</v>
+        <v>56.39</v>
       </c>
       <c r="G6">
         <v>40</v>
       </c>
       <c r="H6">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="I6">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="J6">
         <v>40</v>
       </c>
       <c r="K6">
-        <v>34.5</v>
+        <v>32</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
@@ -737,7 +737,7 @@
         <v>27</v>
       </c>
       <c r="N6">
-        <v>4.469434098808478</v>
+        <v>0</v>
       </c>
       <c r="O6" t="s">
         <v>28</v>

--- a/DECISION/국장_방산_분석.xlsx
+++ b/DECISION/국장_방산_분석.xlsx
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-03-09</t>
+    <t>2026-03-10</t>
   </si>
   <si>
     <t>HANWHA AEROSPACE</t>
@@ -70,37 +70,37 @@
     <t>HANWHA SYSTEMS</t>
   </si>
   <si>
+    <t>KOREA AEROSPACE</t>
+  </si>
+  <si>
+    <t>LIG Nex1</t>
+  </si>
+  <si>
     <t>HYUNDAI ROTEM</t>
   </si>
   <si>
-    <t>KOREA AEROSPACE</t>
-  </si>
-  <si>
-    <t>LIG Nex1</t>
-  </si>
-  <si>
     <t>012450.KS</t>
   </si>
   <si>
     <t>272210.KS</t>
   </si>
   <si>
+    <t>047810.KS</t>
+  </si>
+  <si>
+    <t>079550.KS</t>
+  </si>
+  <si>
     <t>064350.KS</t>
   </si>
   <si>
-    <t>047810.KS</t>
-  </si>
-  <si>
-    <t>079550.KS</t>
-  </si>
-  <si>
     <t>Pattern</t>
   </si>
   <si>
     <t>⛔ 관망하십시오.</t>
   </si>
   <si>
-    <t>🔴 강한 긴축 / 리스크</t>
+    <t>🟠 하락 우위 (긴장 구간)</t>
   </si>
 </sst>
 </file>
@@ -519,28 +519,28 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>1434000</v>
+        <v>1440000</v>
       </c>
       <c r="E2">
-        <v>69.59999999999999</v>
+        <v>69.8</v>
       </c>
       <c r="F2">
-        <v>20</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G2">
         <v>60</v>
       </c>
       <c r="H2">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I2">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="J2">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="K2">
-        <v>42</v>
+        <v>48.9</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -549,7 +549,7 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>32.23518188264562</v>
       </c>
       <c r="O2" t="s">
         <v>28</v>
@@ -566,28 +566,28 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>162700</v>
+        <v>155200</v>
       </c>
       <c r="E3">
-        <v>71.8</v>
+        <v>67.2</v>
       </c>
       <c r="F3">
-        <v>43.22</v>
+        <v>5.79</v>
       </c>
       <c r="G3">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="H3">
+        <v>46</v>
+      </c>
+      <c r="I3">
         <v>53</v>
       </c>
-      <c r="I3">
-        <v>60</v>
-      </c>
       <c r="J3">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="K3">
-        <v>36</v>
+        <v>48.9</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
@@ -596,7 +596,7 @@
         <v>27</v>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>32.23518188264562</v>
       </c>
       <c r="O3" t="s">
         <v>28</v>
@@ -613,28 +613,28 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>215000</v>
+        <v>171800</v>
       </c>
       <c r="E4">
-        <v>54</v>
+        <v>52.7</v>
       </c>
       <c r="F4">
-        <v>-6.72</v>
+        <v>-13.06</v>
       </c>
       <c r="G4">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H4">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="I4">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="J4">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="K4">
-        <v>34.4</v>
+        <v>42.1</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
@@ -643,7 +643,7 @@
         <v>27</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>32.23518188264562</v>
       </c>
       <c r="O4" t="s">
         <v>28</v>
@@ -660,28 +660,28 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>174100</v>
+        <v>755000</v>
       </c>
       <c r="E5">
-        <v>55</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="F5">
-        <v>-9.09</v>
+        <v>14.22</v>
       </c>
       <c r="G5">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H5">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="I5">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="J5">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="K5">
-        <v>33</v>
+        <v>41.9</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
@@ -690,7 +690,7 @@
         <v>27</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>32.23518188264562</v>
       </c>
       <c r="O5" t="s">
         <v>28</v>
@@ -707,28 +707,28 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>796000</v>
+        <v>208000</v>
       </c>
       <c r="E6">
-        <v>81.40000000000001</v>
+        <v>50.6</v>
       </c>
       <c r="F6">
-        <v>56.39</v>
+        <v>-16.47</v>
       </c>
       <c r="G6">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H6">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="I6">
+        <v>53</v>
+      </c>
+      <c r="J6">
         <v>50</v>
       </c>
-      <c r="J6">
-        <v>40</v>
-      </c>
       <c r="K6">
-        <v>32</v>
+        <v>39.9</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
@@ -737,7 +737,7 @@
         <v>27</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>32.23518188264562</v>
       </c>
       <c r="O6" t="s">
         <v>28</v>

--- a/DECISION/국장_방산_분석.xlsx
+++ b/DECISION/국장_방산_분석.xlsx
@@ -64,31 +64,31 @@
     <t>2026-03-10</t>
   </si>
   <si>
+    <t>HANWHA SYSTEMS</t>
+  </si>
+  <si>
     <t>HANWHA AEROSPACE</t>
   </si>
   <si>
-    <t>HANWHA SYSTEMS</t>
+    <t>LIG Nex1</t>
   </si>
   <si>
     <t>KOREA AEROSPACE</t>
   </si>
   <si>
-    <t>LIG Nex1</t>
-  </si>
-  <si>
     <t>HYUNDAI ROTEM</t>
   </si>
   <si>
+    <t>272210.KS</t>
+  </si>
+  <si>
     <t>012450.KS</t>
   </si>
   <si>
-    <t>272210.KS</t>
+    <t>079550.KS</t>
   </si>
   <si>
     <t>047810.KS</t>
-  </si>
-  <si>
-    <t>079550.KS</t>
   </si>
   <si>
     <t>064350.KS</t>
@@ -519,25 +519,25 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>1440000</v>
+        <v>156100</v>
       </c>
       <c r="E2">
-        <v>69.8</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="F2">
-        <v>0.5600000000000001</v>
+        <v>6.41</v>
       </c>
       <c r="G2">
         <v>60</v>
       </c>
       <c r="H2">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="I2">
         <v>53</v>
       </c>
       <c r="J2">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="K2">
         <v>48.9</v>
@@ -549,7 +549,7 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>32.23518188264562</v>
+        <v>32.42054265786911</v>
       </c>
       <c r="O2" t="s">
         <v>28</v>
@@ -566,28 +566,28 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>155200</v>
+        <v>1455000</v>
       </c>
       <c r="E3">
-        <v>67.2</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="F3">
-        <v>5.79</v>
+        <v>1.61</v>
       </c>
       <c r="G3">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H3">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="I3">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="J3">
         <v>50</v>
       </c>
       <c r="K3">
-        <v>48.9</v>
+        <v>47.1</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
@@ -596,7 +596,7 @@
         <v>27</v>
       </c>
       <c r="N3">
-        <v>32.23518188264562</v>
+        <v>32.42054265786911</v>
       </c>
       <c r="O3" t="s">
         <v>28</v>
@@ -613,28 +613,28 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>171800</v>
+        <v>760000</v>
       </c>
       <c r="E4">
-        <v>52.7</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="F4">
-        <v>-13.06</v>
+        <v>14.98</v>
       </c>
       <c r="G4">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H4">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="I4">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="J4">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="K4">
-        <v>42.1</v>
+        <v>43.1</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
@@ -643,7 +643,7 @@
         <v>27</v>
       </c>
       <c r="N4">
-        <v>32.23518188264562</v>
+        <v>32.42054265786911</v>
       </c>
       <c r="O4" t="s">
         <v>28</v>
@@ -660,28 +660,28 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>755000</v>
+        <v>174200</v>
       </c>
       <c r="E5">
-        <v>75.90000000000001</v>
+        <v>53.8</v>
       </c>
       <c r="F5">
-        <v>14.22</v>
+        <v>-11.84</v>
       </c>
       <c r="G5">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H5">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="I5">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="J5">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="K5">
-        <v>41.9</v>
+        <v>42.1</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
@@ -690,7 +690,7 @@
         <v>27</v>
       </c>
       <c r="N5">
-        <v>32.23518188264562</v>
+        <v>32.42054265786911</v>
       </c>
       <c r="O5" t="s">
         <v>28</v>
@@ -707,13 +707,13 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>208000</v>
+        <v>208500</v>
       </c>
       <c r="E6">
-        <v>50.6</v>
+        <v>50.8</v>
       </c>
       <c r="F6">
-        <v>-16.47</v>
+        <v>-16.27</v>
       </c>
       <c r="G6">
         <v>30</v>
@@ -737,7 +737,7 @@
         <v>27</v>
       </c>
       <c r="N6">
-        <v>32.23518188264562</v>
+        <v>32.42054265786911</v>
       </c>
       <c r="O6" t="s">
         <v>28</v>

--- a/DECISION/국장_방산_분석.xlsx
+++ b/DECISION/국장_방산_분석.xlsx
@@ -61,46 +61,46 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-03-10</t>
+    <t>2026-03-11</t>
   </si>
   <si>
     <t>HANWHA SYSTEMS</t>
   </si>
   <si>
+    <t>KOREA AEROSPACE</t>
+  </si>
+  <si>
+    <t>HYUNDAI ROTEM</t>
+  </si>
+  <si>
     <t>HANWHA AEROSPACE</t>
   </si>
   <si>
     <t>LIG Nex1</t>
   </si>
   <si>
-    <t>KOREA AEROSPACE</t>
-  </si>
-  <si>
-    <t>HYUNDAI ROTEM</t>
-  </si>
-  <si>
     <t>272210.KS</t>
   </si>
   <si>
+    <t>047810.KS</t>
+  </si>
+  <si>
+    <t>064350.KS</t>
+  </si>
+  <si>
     <t>012450.KS</t>
   </si>
   <si>
     <t>079550.KS</t>
   </si>
   <si>
-    <t>047810.KS</t>
-  </si>
-  <si>
-    <t>064350.KS</t>
-  </si>
-  <si>
     <t>Pattern</t>
   </si>
   <si>
     <t>⛔ 관망하십시오.</t>
   </si>
   <si>
-    <t>🟠 하락 우위 (긴장 구간)</t>
+    <t>⚪ 중립 구간</t>
   </si>
 </sst>
 </file>
@@ -519,13 +519,13 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>156100</v>
+        <v>149200</v>
       </c>
       <c r="E2">
-        <v>67.59999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="F2">
-        <v>6.41</v>
+        <v>28.62</v>
       </c>
       <c r="G2">
         <v>60</v>
@@ -534,13 +534,13 @@
         <v>46</v>
       </c>
       <c r="I2">
+        <v>60</v>
+      </c>
+      <c r="J2">
         <v>53</v>
       </c>
-      <c r="J2">
-        <v>50</v>
-      </c>
       <c r="K2">
-        <v>48.9</v>
+        <v>55</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -549,7 +549,7 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>32.42054265786911</v>
+        <v>43.44936356612781</v>
       </c>
       <c r="O2" t="s">
         <v>28</v>
@@ -566,28 +566,28 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>1455000</v>
+        <v>176700</v>
       </c>
       <c r="E3">
-        <v>70.40000000000001</v>
+        <v>50</v>
       </c>
       <c r="F3">
-        <v>1.61</v>
+        <v>11.48</v>
       </c>
       <c r="G3">
         <v>50</v>
       </c>
       <c r="H3">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="I3">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="J3">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="K3">
-        <v>47.1</v>
+        <v>54.4</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
@@ -596,7 +596,7 @@
         <v>27</v>
       </c>
       <c r="N3">
-        <v>32.42054265786911</v>
+        <v>43.44936356612781</v>
       </c>
       <c r="O3" t="s">
         <v>28</v>
@@ -613,28 +613,28 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>760000</v>
+        <v>207000</v>
       </c>
       <c r="E4">
-        <v>76.59999999999999</v>
+        <v>51.8</v>
       </c>
       <c r="F4">
-        <v>14.98</v>
+        <v>2.48</v>
       </c>
       <c r="G4">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H4">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="I4">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="J4">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="K4">
-        <v>43.1</v>
+        <v>47.4</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
@@ -643,7 +643,7 @@
         <v>27</v>
       </c>
       <c r="N4">
-        <v>32.42054265786911</v>
+        <v>43.44936356612781</v>
       </c>
       <c r="O4" t="s">
         <v>28</v>
@@ -660,28 +660,28 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>174200</v>
+        <v>1457000</v>
       </c>
       <c r="E5">
-        <v>53.8</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="F5">
-        <v>-11.84</v>
+        <v>10.13</v>
       </c>
       <c r="G5">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H5">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="I5">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="J5">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="K5">
-        <v>42.1</v>
+        <v>44</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
@@ -690,7 +690,7 @@
         <v>27</v>
       </c>
       <c r="N5">
-        <v>32.42054265786911</v>
+        <v>43.44936356612781</v>
       </c>
       <c r="O5" t="s">
         <v>28</v>
@@ -707,28 +707,28 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>208500</v>
+        <v>752000</v>
       </c>
       <c r="E6">
-        <v>50.8</v>
+        <v>75.3</v>
       </c>
       <c r="F6">
-        <v>-16.27</v>
+        <v>21.49</v>
       </c>
       <c r="G6">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H6">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="I6">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="J6">
         <v>50</v>
       </c>
       <c r="K6">
-        <v>39.9</v>
+        <v>42.4</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
@@ -737,7 +737,7 @@
         <v>27</v>
       </c>
       <c r="N6">
-        <v>32.42054265786911</v>
+        <v>43.44936356612781</v>
       </c>
       <c r="O6" t="s">
         <v>28</v>

--- a/DECISION/국장_방산_분석.xlsx
+++ b/DECISION/국장_방산_분석.xlsx
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-03-11</t>
+    <t>2026-03-12</t>
   </si>
   <si>
     <t>HANWHA SYSTEMS</t>
@@ -70,28 +70,28 @@
     <t>KOREA AEROSPACE</t>
   </si>
   <si>
+    <t>HANWHA AEROSPACE</t>
+  </si>
+  <si>
+    <t>LIG Nex1</t>
+  </si>
+  <si>
     <t>HYUNDAI ROTEM</t>
   </si>
   <si>
-    <t>HANWHA AEROSPACE</t>
-  </si>
-  <si>
-    <t>LIG Nex1</t>
-  </si>
-  <si>
     <t>272210.KS</t>
   </si>
   <si>
     <t>047810.KS</t>
   </si>
   <si>
+    <t>012450.KS</t>
+  </si>
+  <si>
+    <t>079550.KS</t>
+  </si>
+  <si>
     <t>064350.KS</t>
-  </si>
-  <si>
-    <t>012450.KS</t>
-  </si>
-  <si>
-    <t>079550.KS</t>
   </si>
   <si>
     <t>Pattern</t>
@@ -519,28 +519,28 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>149200</v>
+        <v>152300</v>
       </c>
       <c r="E2">
-        <v>65.59999999999999</v>
+        <v>65.3</v>
       </c>
       <c r="F2">
-        <v>28.62</v>
+        <v>0.99</v>
       </c>
       <c r="G2">
         <v>60</v>
       </c>
       <c r="H2">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="I2">
         <v>60</v>
       </c>
       <c r="J2">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="K2">
-        <v>55</v>
+        <v>54.5</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -549,7 +549,7 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>43.44936356612781</v>
+        <v>41.74287521812095</v>
       </c>
       <c r="O2" t="s">
         <v>28</v>
@@ -566,28 +566,28 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>176700</v>
+        <v>179800</v>
       </c>
       <c r="E3">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F3">
-        <v>11.48</v>
+        <v>0.45</v>
       </c>
       <c r="G3">
         <v>50</v>
       </c>
       <c r="H3">
+        <v>76</v>
+      </c>
+      <c r="I3">
         <v>60</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>66</v>
       </c>
-      <c r="J3">
-        <v>70</v>
-      </c>
       <c r="K3">
-        <v>54.4</v>
+        <v>51.5</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
@@ -596,7 +596,7 @@
         <v>27</v>
       </c>
       <c r="N3">
-        <v>43.44936356612781</v>
+        <v>41.74287521812095</v>
       </c>
       <c r="O3" t="s">
         <v>28</v>
@@ -613,28 +613,28 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>207000</v>
+        <v>1465000</v>
       </c>
       <c r="E4">
-        <v>51.8</v>
+        <v>69.2</v>
       </c>
       <c r="F4">
-        <v>2.48</v>
+        <v>6.08</v>
       </c>
       <c r="G4">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="H4">
         <v>53</v>
       </c>
       <c r="I4">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="J4">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="K4">
-        <v>47.4</v>
+        <v>48.9</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
@@ -643,7 +643,7 @@
         <v>27</v>
       </c>
       <c r="N4">
-        <v>43.44936356612781</v>
+        <v>41.74287521812095</v>
       </c>
       <c r="O4" t="s">
         <v>28</v>
@@ -660,28 +660,28 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>1457000</v>
+        <v>755000</v>
       </c>
       <c r="E5">
-        <v>72.90000000000001</v>
+        <v>74.5</v>
       </c>
       <c r="F5">
-        <v>10.13</v>
+        <v>-1.05</v>
       </c>
       <c r="G5">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H5">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="I5">
         <v>40</v>
       </c>
       <c r="J5">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="K5">
-        <v>44</v>
+        <v>40.5</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
@@ -690,7 +690,7 @@
         <v>27</v>
       </c>
       <c r="N5">
-        <v>43.44936356612781</v>
+        <v>41.74287521812095</v>
       </c>
       <c r="O5" t="s">
         <v>28</v>
@@ -707,28 +707,28 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>752000</v>
+        <v>206000</v>
       </c>
       <c r="E6">
-        <v>75.3</v>
+        <v>48.7</v>
       </c>
       <c r="F6">
-        <v>21.49</v>
+        <v>-8.65</v>
       </c>
       <c r="G6">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H6">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="I6">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="J6">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="K6">
-        <v>42.4</v>
+        <v>39.7</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
@@ -737,7 +737,7 @@
         <v>27</v>
       </c>
       <c r="N6">
-        <v>43.44936356612781</v>
+        <v>41.74287521812095</v>
       </c>
       <c r="O6" t="s">
         <v>28</v>

--- a/DECISION/국장_방산_분석.xlsx
+++ b/DECISION/국장_방산_분석.xlsx
@@ -549,7 +549,7 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>41.74287521812095</v>
+        <v>41.81508460778518</v>
       </c>
       <c r="O2" t="s">
         <v>28</v>
@@ -596,7 +596,7 @@
         <v>27</v>
       </c>
       <c r="N3">
-        <v>41.74287521812095</v>
+        <v>41.81508460778518</v>
       </c>
       <c r="O3" t="s">
         <v>28</v>
@@ -643,7 +643,7 @@
         <v>27</v>
       </c>
       <c r="N4">
-        <v>41.74287521812095</v>
+        <v>41.81508460778518</v>
       </c>
       <c r="O4" t="s">
         <v>28</v>
@@ -690,7 +690,7 @@
         <v>27</v>
       </c>
       <c r="N5">
-        <v>41.74287521812095</v>
+        <v>41.81508460778518</v>
       </c>
       <c r="O5" t="s">
         <v>28</v>
@@ -737,7 +737,7 @@
         <v>27</v>
       </c>
       <c r="N6">
-        <v>41.74287521812095</v>
+        <v>41.81508460778518</v>
       </c>
       <c r="O6" t="s">
         <v>28</v>

--- a/DECISION/국장_방산_분석.xlsx
+++ b/DECISION/국장_방산_분석.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="30">
   <si>
     <t>날짜</t>
   </si>
@@ -61,7 +61,16 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-03-12</t>
+    <t>2026-04-08</t>
+  </si>
+  <si>
+    <t>HANWHA AEROSPACE</t>
+  </si>
+  <si>
+    <t>HYUNDAI ROTEM</t>
+  </si>
+  <si>
+    <t>LIG Nex1</t>
   </si>
   <si>
     <t>HANWHA SYSTEMS</t>
@@ -70,13 +79,13 @@
     <t>KOREA AEROSPACE</t>
   </si>
   <si>
-    <t>HANWHA AEROSPACE</t>
-  </si>
-  <si>
-    <t>LIG Nex1</t>
-  </si>
-  <si>
-    <t>HYUNDAI ROTEM</t>
+    <t>012450.KS</t>
+  </si>
+  <si>
+    <t>064350.KS</t>
+  </si>
+  <si>
+    <t>079550.KS</t>
   </si>
   <si>
     <t>272210.KS</t>
@@ -85,22 +94,16 @@
     <t>047810.KS</t>
   </si>
   <si>
-    <t>012450.KS</t>
-  </si>
-  <si>
-    <t>079550.KS</t>
-  </si>
-  <si>
-    <t>064350.KS</t>
-  </si>
-  <si>
     <t>Pattern</t>
   </si>
   <si>
+    <t>📈 매수 관찰 구간입니다.</t>
+  </si>
+  <si>
     <t>⛔ 관망하십시오.</t>
   </si>
   <si>
-    <t>⚪ 중립 구간</t>
+    <t>🟢 상승 우위 (다소 완화)</t>
   </si>
 </sst>
 </file>
@@ -519,28 +522,28 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>152300</v>
+        <v>1466000</v>
       </c>
       <c r="E2">
-        <v>65.3</v>
+        <v>56.2</v>
       </c>
       <c r="F2">
-        <v>0.99</v>
+        <v>10.14</v>
       </c>
       <c r="G2">
         <v>60</v>
       </c>
       <c r="H2">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="I2">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="J2">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K2">
-        <v>54.5</v>
+        <v>63.2</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -549,10 +552,10 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>41.81508460778518</v>
+        <v>66.57973643566133</v>
       </c>
       <c r="O2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -566,40 +569,40 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>179800</v>
+        <v>205000</v>
       </c>
       <c r="E3">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="F3">
-        <v>0.45</v>
+        <v>8.52</v>
       </c>
       <c r="G3">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H3">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="I3">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="J3">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="K3">
-        <v>51.5</v>
+        <v>59.2</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
       </c>
       <c r="M3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N3">
-        <v>41.81508460778518</v>
+        <v>66.57973643566133</v>
       </c>
       <c r="O3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -613,40 +616,40 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>1465000</v>
+        <v>827000</v>
       </c>
       <c r="E4">
-        <v>69.2</v>
+        <v>60.4</v>
       </c>
       <c r="F4">
-        <v>6.08</v>
+        <v>4.16</v>
       </c>
       <c r="G4">
         <v>60</v>
       </c>
       <c r="H4">
+        <v>66</v>
+      </c>
+      <c r="I4">
         <v>53</v>
-      </c>
-      <c r="I4">
-        <v>46</v>
       </c>
       <c r="J4">
         <v>46</v>
       </c>
       <c r="K4">
-        <v>48.9</v>
+        <v>59.2</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
       </c>
       <c r="M4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N4">
-        <v>41.81508460778518</v>
+        <v>66.57973643566133</v>
       </c>
       <c r="O4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -660,40 +663,40 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>755000</v>
+        <v>130200</v>
       </c>
       <c r="E5">
-        <v>74.5</v>
+        <v>44</v>
       </c>
       <c r="F5">
-        <v>-1.05</v>
+        <v>1.01</v>
       </c>
       <c r="G5">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H5">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="I5">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="J5">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="K5">
-        <v>40.5</v>
+        <v>58.2</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
       </c>
       <c r="M5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N5">
-        <v>41.81508460778518</v>
+        <v>66.57973643566133</v>
       </c>
       <c r="O5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -707,40 +710,40 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>206000</v>
+        <v>188300</v>
       </c>
       <c r="E6">
-        <v>48.7</v>
+        <v>49.2</v>
       </c>
       <c r="F6">
-        <v>-8.65</v>
+        <v>0.27</v>
       </c>
       <c r="G6">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H6">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="I6">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="J6">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="K6">
-        <v>39.7</v>
+        <v>57.4</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
       </c>
       <c r="M6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N6">
-        <v>41.81508460778518</v>
+        <v>66.57973643566133</v>
       </c>
       <c r="O6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/DECISION/국장_방산_분석.xlsx
+++ b/DECISION/국장_방산_분석.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="29">
   <si>
     <t>날짜</t>
   </si>
@@ -61,49 +61,46 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-04-08</t>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>HYUNDAI ROTEM</t>
+  </si>
+  <si>
+    <t>KOREA AEROSPACE</t>
+  </si>
+  <si>
+    <t>HANWHA SYSTEMS</t>
+  </si>
+  <si>
+    <t>LIG Defense&amp;Aerospace</t>
   </si>
   <si>
     <t>HANWHA AEROSPACE</t>
   </si>
   <si>
-    <t>HYUNDAI ROTEM</t>
-  </si>
-  <si>
-    <t>LIG Nex1</t>
-  </si>
-  <si>
-    <t>HANWHA SYSTEMS</t>
-  </si>
-  <si>
-    <t>KOREA AEROSPACE</t>
+    <t>064350.KS</t>
+  </si>
+  <si>
+    <t>047810.KS</t>
+  </si>
+  <si>
+    <t>272210.KS</t>
+  </si>
+  <si>
+    <t>079550.KS</t>
   </si>
   <si>
     <t>012450.KS</t>
   </si>
   <si>
-    <t>064350.KS</t>
-  </si>
-  <si>
-    <t>079550.KS</t>
-  </si>
-  <si>
-    <t>272210.KS</t>
-  </si>
-  <si>
-    <t>047810.KS</t>
-  </si>
-  <si>
     <t>Pattern</t>
   </si>
   <si>
-    <t>📈 매수 관찰 구간입니다.</t>
-  </si>
-  <si>
     <t>⛔ 관망하십시오.</t>
   </si>
   <si>
-    <t>🟢 상승 우위 (다소 완화)</t>
+    <t>⚪ 중립 구간</t>
   </si>
 </sst>
 </file>
@@ -522,28 +519,28 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>1466000</v>
+        <v>237000</v>
       </c>
       <c r="E2">
-        <v>56.2</v>
+        <v>63</v>
       </c>
       <c r="F2">
-        <v>10.14</v>
+        <v>-3.07</v>
       </c>
       <c r="G2">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H2">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="I2">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="J2">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="K2">
-        <v>63.2</v>
+        <v>55.1</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -552,10 +549,10 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>66.57973643566133</v>
+        <v>59.14876667115259</v>
       </c>
       <c r="O2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -569,40 +566,40 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>205000</v>
+        <v>171100</v>
       </c>
       <c r="E3">
-        <v>59</v>
+        <v>32.3</v>
       </c>
       <c r="F3">
-        <v>8.52</v>
+        <v>1.85</v>
       </c>
       <c r="G3">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="H3">
+        <v>73</v>
+      </c>
+      <c r="I3">
         <v>63</v>
       </c>
-      <c r="I3">
-        <v>53</v>
-      </c>
       <c r="J3">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K3">
-        <v>59.2</v>
+        <v>48.9</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
       </c>
       <c r="M3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N3">
+        <v>59.14876667115259</v>
+      </c>
+      <c r="O3" t="s">
         <v>28</v>
-      </c>
-      <c r="N3">
-        <v>66.57973643566133</v>
-      </c>
-      <c r="O3" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -616,40 +613,40 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>827000</v>
+        <v>117300</v>
       </c>
       <c r="E4">
-        <v>60.4</v>
+        <v>29.4</v>
       </c>
       <c r="F4">
-        <v>4.16</v>
+        <v>-2.17</v>
       </c>
       <c r="G4">
+        <v>10</v>
+      </c>
+      <c r="H4">
+        <v>63</v>
+      </c>
+      <c r="I4">
+        <v>70</v>
+      </c>
+      <c r="J4">
         <v>60</v>
       </c>
-      <c r="H4">
-        <v>66</v>
-      </c>
-      <c r="I4">
-        <v>53</v>
-      </c>
-      <c r="J4">
-        <v>46</v>
-      </c>
       <c r="K4">
-        <v>59.2</v>
+        <v>48.7</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
       </c>
       <c r="M4" t="s">
+        <v>27</v>
+      </c>
+      <c r="N4">
+        <v>59.14876667115259</v>
+      </c>
+      <c r="O4" t="s">
         <v>28</v>
-      </c>
-      <c r="N4">
-        <v>66.57973643566133</v>
-      </c>
-      <c r="O4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -663,40 +660,40 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>130200</v>
+        <v>927000</v>
       </c>
       <c r="E5">
-        <v>44</v>
+        <v>53.6</v>
       </c>
       <c r="F5">
-        <v>1.01</v>
+        <v>-0.64</v>
       </c>
       <c r="G5">
         <v>30</v>
       </c>
       <c r="H5">
+        <v>53</v>
+      </c>
+      <c r="I5">
+        <v>46</v>
+      </c>
+      <c r="J5">
         <v>60</v>
       </c>
-      <c r="I5">
-        <v>73</v>
-      </c>
-      <c r="J5">
-        <v>63</v>
-      </c>
       <c r="K5">
-        <v>58.2</v>
+        <v>45.1</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
       </c>
       <c r="M5" t="s">
+        <v>27</v>
+      </c>
+      <c r="N5">
+        <v>59.14876667115259</v>
+      </c>
+      <c r="O5" t="s">
         <v>28</v>
-      </c>
-      <c r="N5">
-        <v>66.57973643566133</v>
-      </c>
-      <c r="O5" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -710,40 +707,40 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>188300</v>
+        <v>1327000</v>
       </c>
       <c r="E6">
-        <v>49.2</v>
+        <v>31.7</v>
       </c>
       <c r="F6">
-        <v>0.27</v>
+        <v>-4.87</v>
       </c>
       <c r="G6">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="I6">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="J6">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="K6">
-        <v>57.4</v>
+        <v>44.1</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
       </c>
       <c r="M6" t="s">
+        <v>27</v>
+      </c>
+      <c r="N6">
+        <v>59.14876667115259</v>
+      </c>
+      <c r="O6" t="s">
         <v>28</v>
-      </c>
-      <c r="N6">
-        <v>66.57973643566133</v>
-      </c>
-      <c r="O6" t="s">
-        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/DECISION/국장_방산_분석.xlsx
+++ b/DECISION/국장_방산_분석.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="30">
   <si>
     <t>날짜</t>
   </si>
@@ -61,46 +61,49 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-05-07</t>
+    <t>2026-06-07</t>
   </si>
   <si>
     <t>HYUNDAI ROTEM</t>
   </si>
   <si>
+    <t>LIG Defense&amp;Aerospace</t>
+  </si>
+  <si>
+    <t>HANWHA SYSTEMS</t>
+  </si>
+  <si>
     <t>KOREA AEROSPACE</t>
   </si>
   <si>
-    <t>HANWHA SYSTEMS</t>
-  </si>
-  <si>
-    <t>LIG Defense&amp;Aerospace</t>
-  </si>
-  <si>
     <t>HANWHA AEROSPACE</t>
   </si>
   <si>
     <t>064350.KS</t>
   </si>
   <si>
+    <t>079550.KS</t>
+  </si>
+  <si>
+    <t>272210.KS</t>
+  </si>
+  <si>
     <t>047810.KS</t>
   </si>
   <si>
-    <t>272210.KS</t>
-  </si>
-  <si>
-    <t>079550.KS</t>
-  </si>
-  <si>
     <t>012450.KS</t>
   </si>
   <si>
     <t>Pattern</t>
   </si>
   <si>
+    <t>🤏 바닥권 접근 구간입니다.</t>
+  </si>
+  <si>
     <t>⛔ 관망하십시오.</t>
   </si>
   <si>
-    <t>⚪ 중립 구간</t>
+    <t>🔴 강한 긴축 / 리스크</t>
   </si>
 </sst>
 </file>
@@ -519,28 +522,28 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>237000</v>
+        <v>191400</v>
       </c>
       <c r="E2">
-        <v>63</v>
+        <v>38.7</v>
       </c>
       <c r="F2">
-        <v>-3.07</v>
+        <v>-7.09</v>
       </c>
       <c r="G2">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="H2">
         <v>53</v>
       </c>
       <c r="I2">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="J2">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="K2">
-        <v>55.1</v>
+        <v>38.9</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -549,10 +552,10 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>59.14876667115259</v>
+        <v>13.11002090356014</v>
       </c>
       <c r="O2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -566,40 +569,40 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>171100</v>
+        <v>726000</v>
       </c>
       <c r="E3">
-        <v>32.3</v>
+        <v>31.3</v>
       </c>
       <c r="F3">
-        <v>1.85</v>
+        <v>-15.19</v>
       </c>
       <c r="G3">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H3">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="I3">
+        <v>70</v>
+      </c>
+      <c r="J3">
         <v>63</v>
       </c>
-      <c r="J3">
-        <v>73</v>
-      </c>
       <c r="K3">
-        <v>48.9</v>
+        <v>34.9</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
       </c>
       <c r="M3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N3">
-        <v>59.14876667115259</v>
+        <v>13.11002090356014</v>
       </c>
       <c r="O3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -613,40 +616,40 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>117300</v>
+        <v>94600</v>
       </c>
       <c r="E4">
-        <v>29.4</v>
+        <v>29.3</v>
       </c>
       <c r="F4">
-        <v>-2.17</v>
+        <v>-10.67</v>
       </c>
       <c r="G4">
         <v>10</v>
       </c>
       <c r="H4">
+        <v>50</v>
+      </c>
+      <c r="I4">
         <v>63</v>
-      </c>
-      <c r="I4">
-        <v>70</v>
       </c>
       <c r="J4">
         <v>60</v>
       </c>
       <c r="K4">
-        <v>48.7</v>
+        <v>32.1</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
       </c>
       <c r="M4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N4">
-        <v>59.14876667115259</v>
+        <v>13.11002090356014</v>
       </c>
       <c r="O4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -660,28 +663,28 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>927000</v>
+        <v>139000</v>
       </c>
       <c r="E5">
-        <v>53.6</v>
+        <v>23.9</v>
       </c>
       <c r="F5">
-        <v>-0.64</v>
+        <v>-17.21</v>
       </c>
       <c r="G5">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="I5">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="J5">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="K5">
-        <v>45.1</v>
+        <v>31.9</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
@@ -690,10 +693,10 @@
         <v>27</v>
       </c>
       <c r="N5">
-        <v>59.14876667115259</v>
+        <v>13.11002090356014</v>
       </c>
       <c r="O5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -707,40 +710,40 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>1327000</v>
+        <v>1049000</v>
       </c>
       <c r="E6">
-        <v>31.7</v>
+        <v>19.6</v>
       </c>
       <c r="F6">
-        <v>-4.87</v>
+        <v>-12.58</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="I6">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="J6">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="K6">
-        <v>44.1</v>
+        <v>25.1</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
       </c>
       <c r="M6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N6">
-        <v>59.14876667115259</v>
+        <v>13.11002090356014</v>
       </c>
       <c r="O6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
